--- a/public/assets/files/Excel_Demo-02/SISB_USEP_DEMO-2.xlsx
+++ b/public/assets/files/Excel_Demo-02/SISB_USEP_DEMO-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/genevieve_guex_epfl_ch/Documents/Documents/SISB_Presentations/SISB-Apero-Slidev/public/assets/files/Excel_Demo-02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1185" documentId="8_{B86F2B6C-3DE1-486D-B3D3-0A1863A11CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81583113-3E64-4692-814B-A7B7C20DC27C}"/>
+  <xr:revisionPtr revIDLastSave="1375" documentId="8_{B86F2B6C-3DE1-486D-B3D3-0A1863A11CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{966E1D2C-4C9B-4407-92F6-8667675C4E53}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{537DF2C6-54A6-4649-8875-CD01F068054D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{537DF2C6-54A6-4649-8875-CD01F068054D}"/>
   </bookViews>
   <sheets>
     <sheet name="USEP_2026" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="USEP_Demo" sheetId="7" r:id="rId5"/>
     <sheet name="USEP_Demo_01" sheetId="3" r:id="rId6"/>
     <sheet name="USEP_Demo_02" sheetId="4" r:id="rId7"/>
+    <sheet name="Feuil2" sheetId="9" r:id="rId8"/>
+    <sheet name="Feuil3" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="PlageDates2026">USEP_Demo!$E$1:$P$1</definedName>
@@ -29,7 +31,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -54,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="105">
   <si>
     <t>N° Indicateur</t>
   </si>
@@ -358,6 +360,43 @@
   <si>
     <t>différence entre le nombre le plus haut et nombre le plus bas (pourcentage)?</t>
   </si>
+  <si>
+    <t>Valeurs maximum</t>
+  </si>
+  <si>
+    <t>Valeurs minimum</t>
+  </si>
+  <si>
+    <t>Descriptif</t>
+  </si>
+  <si>
+    <t>Cette opération s'appelle</t>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="26"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>pivoter les données</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -371,7 +410,7 @@
     <numFmt numFmtId="167" formatCode="mmmm"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -486,6 +525,26 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -513,7 +572,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -663,13 +722,109 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -795,20 +950,17 @@
     <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -817,16 +969,12 @@
     <xf numFmtId="167" fontId="14" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -859,11 +1007,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -886,7 +1031,7 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -899,22 +1044,314 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{D0C2D436-22CC-4622-BFAB-EE73B1162312}"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -1615,35 +2052,6 @@
                   <c:y val="-1.5076129469937749E-2"/>
                 </c:manualLayout>
               </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:pPr>
-                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                        <a:solidFill>
-                          <a:schemeClr val="tx1">
-                            <a:lumMod val="65000"/>
-                            <a:lumOff val="35000"/>
-                          </a:schemeClr>
-                        </a:solidFill>
-                        <a:latin typeface="+mn-lt"/>
-                        <a:ea typeface="+mn-ea"/>
-                        <a:cs typeface="+mn-cs"/>
-                      </a:defRPr>
-                    </a:pPr>
-                    <a:r>
-                      <a:rPr lang="en-US" b="1">
-                        <a:solidFill>
-                          <a:schemeClr val="accent4"/>
-                        </a:solidFill>
-                      </a:rPr>
-                      <a:t>R² = 0.8106</a:t>
-                    </a:r>
-                  </a:p>
-                </c:rich>
-              </c:tx>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -12902,6 +13310,972 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>544285</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>122460</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>108857</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Graphique 17" descr="Ligne fléchée : incurvée sens des aiguilles d’une montre avec un remplissage uni">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5158A319-C108-4495-A44A-86C2AB68F9ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="18913928" y="2217960"/>
+          <a:ext cx="2966358" cy="2612575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>149678</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>68037</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>193365</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>47751</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C1F0B91-AD9E-2D4D-CE8D-CA850B1E7512}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10355035" y="4708073"/>
+          <a:ext cx="10929401" cy="10266714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>95251</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>13608</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>40470</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{736E4A92-210A-C428-1A62-34EF8345D259}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="775608" y="1251858"/>
+          <a:ext cx="18288000" cy="2680255"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>653143</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>68036</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>54429</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C6D51A3-158D-8023-3E2B-5F039D892ED3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8817429" y="1864179"/>
+          <a:ext cx="10287000" cy="2122714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent5"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>68036</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>163286</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>68037</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1F3BE18-40B3-4F40-B585-44DEDB319674}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20478750" y="4694464"/>
+          <a:ext cx="775607" cy="10341430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent5"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>386143</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>21856</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>353785</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>40820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Flèche : droite 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10CECEA5-7F0E-3759-6B53-F258AF65C50A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="21477214" y="4811570"/>
+          <a:ext cx="648000" cy="468000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B0F0"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="lt1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>435427</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>149677</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>122465</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="ZoneTexte 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B113FC39-2EFD-D710-88FD-53763AE4CD84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22206856" y="4789713"/>
+          <a:ext cx="3537857" cy="421823"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent5"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-CH" sz="2400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>une ligne - une valeur</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>388865</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>106221</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>356507</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>125185</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Flèche : droite 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2928293-6B3A-40C9-9BDC-C1EED0899C0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="21479936" y="5195292"/>
+          <a:ext cx="648000" cy="468000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B0F0"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="lt1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>438149</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>84364</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>574221</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="ZoneTexte 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3EC3FCA-0A24-446D-B4D3-1020B8689957}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22209578" y="5173435"/>
+          <a:ext cx="3537857" cy="421823"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent5"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-CH" sz="2400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>une ligne - une valeur</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>522515</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>19048</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>182337</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>427264</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="ZoneTexte 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{268A69C8-4130-4873-8766-4EF8CDCAFAD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22293944" y="5557155"/>
+          <a:ext cx="3061607" cy="979716"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent5"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-CH" sz="2400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>...</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>653143</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>54429</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>122465</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3765E79-B4A7-4A0E-9B2B-A7F54490BC97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8817429" y="1251857"/>
+          <a:ext cx="10287000" cy="517072"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent5"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>615043</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>29936</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>70758</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangle 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{074897D7-62A4-455C-A64D-DADD1FA5D138}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19665043" y="4697185"/>
+          <a:ext cx="775607" cy="10341430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent5"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-CH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>587828</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>95246</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>261257</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Graphique 16" descr="Ligne fléchée : incurvée sens des aiguilles d’une montre avec un remplissage uni">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0D6BD04-2BD1-45CD-81C1-BB816C620766}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="18957471" y="1142996"/>
+          <a:ext cx="1714500" cy="3741968"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>68035</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>68036</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3237168" cy="918200"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="ZoneTexte 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DBA7D67-0E99-101A-EC62-6BFD106C7EB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19798392" y="1115786"/>
+          <a:ext cx="3237168" cy="918200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-CH" sz="2800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>toutes les dates</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-CH" sz="2800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>dans une colonne</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>315685</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2723</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3237168" cy="1331134"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="ZoneTexte 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CC8E72F-1F39-449A-A626-1A25D310437A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21406756" y="2547259"/>
+          <a:ext cx="3237168" cy="1331134"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-CH" sz="2800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>toutes les valeurs</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="fr-CH" sz="2800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="fr-CH" sz="2800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>récoltées</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-CH" sz="2800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>dans une colonne</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
@@ -14210,7 +15584,7 @@
     <dataField name="Variation mois précédent" fld="3" showDataAs="percentDiff" baseField="2" baseItem="1048828" numFmtId="168"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="6">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -14219,7 +15593,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -14228,7 +15602,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -14237,7 +15611,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="14">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -14246,7 +15620,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="13">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -14258,7 +15632,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="12">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -14270,7 +15644,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="11">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -14284,7 +15658,211 @@
     </format>
   </formats>
   <conditionalFormats count="12">
-    <conditionalFormat priority="12">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+            <reference field="2" count="8">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+            <reference field="2" count="8">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="3">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="9">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="4">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="9">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="5">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="2" count="9">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="6">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="2" count="9">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="7">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+            <reference field="2" count="12">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="8">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="12">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="9">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -14293,6 +15871,34 @@
             </reference>
             <reference field="0" count="1" selected="0">
               <x v="0"/>
+            </reference>
+            <reference field="2" count="12">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="10">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="2"/>
             </reference>
             <reference field="2" count="12">
               <x v="0"/>
@@ -14340,35 +15946,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="10">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-            <reference field="2" count="12">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="9">
+    <conditionalFormat priority="12">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -14396,210 +15974,6 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="8">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="2" count="12">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="7">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-            <reference field="2" count="12">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="6">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="2" count="9">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="5">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="2" count="9">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="4">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="2" count="9">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="3">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="2" count="9">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="2">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-            <reference field="2" count="8">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="1">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-            <reference field="2" count="8">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
   </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight19" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -14611,6 +15985,28 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EC91FF0-6FB2-448B-B020-FF75E4912B6E}" name="LongFormat" displayName="LongFormat" ref="B2:G38" totalsRowShown="0" headerRowDxfId="7" dataDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="B2:G38" xr:uid="{9EC91FF0-6FB2-448B-B020-FF75E4912B6E}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{C3F457BA-E1FD-461F-B39D-B29DC7AF5511}" name="N° Indicateur" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{A854F890-2B20-4D64-B269-231139DE3A94}" name="Indicateur" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{28DB4D8B-FF90-4194-8747-A51F6B5601E3}" name="Descriptif" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{0DC2BAB9-CC31-4FB7-A47D-2F415DC936A9}" name="Équipe" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{C116F4D2-1610-497E-A207-37C7A65204A5}" name="Date" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{CD71C008-A581-4C92-AD38-D292BA862EDC}" name="Valeur" dataDxfId="1" dataCellStyle="Milliers"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14930,691 +16326,632 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3EA253C-11C5-4493-9357-287321BBEF02}">
-  <dimension ref="A1:U55"/>
+  <dimension ref="B2:V56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="47.1640625" customWidth="1"/>
-    <col min="4" max="4" width="40.5" customWidth="1"/>
-    <col min="20" max="20" width="16.33203125" customWidth="1"/>
-    <col min="21" max="21" width="88.6640625" customWidth="1"/>
+    <col min="4" max="4" width="47.1640625" customWidth="1"/>
+    <col min="5" max="5" width="40.5" customWidth="1"/>
+    <col min="21" max="21" width="16.33203125" customWidth="1"/>
+    <col min="22" max="22" width="88.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+    <row r="2" spans="2:22" ht="27" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="C2" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="D2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="E2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="52">
+      <c r="F2" s="52">
         <v>46053</v>
       </c>
-      <c r="F1" s="52">
+      <c r="G2" s="52">
         <v>46081</v>
       </c>
-      <c r="G1" s="52">
+      <c r="H2" s="52">
         <v>46112</v>
       </c>
-      <c r="H1" s="52">
+      <c r="I2" s="52">
         <v>46142</v>
       </c>
-      <c r="I1" s="52">
+      <c r="J2" s="52">
         <v>46173</v>
       </c>
-      <c r="J1" s="52">
+      <c r="K2" s="52">
         <v>46203</v>
       </c>
-      <c r="K1" s="52">
+      <c r="L2" s="52">
         <v>46234</v>
       </c>
-      <c r="L1" s="52">
+      <c r="M2" s="52">
         <v>46265</v>
       </c>
-      <c r="M1" s="52">
+      <c r="N2" s="52">
         <v>46295</v>
       </c>
-      <c r="N1" s="52">
+      <c r="O2" s="52">
         <v>46326</v>
       </c>
-      <c r="O1" s="52">
+      <c r="P2" s="52">
         <v>46356</v>
       </c>
-      <c r="P1" s="52">
+      <c r="Q2" s="52">
         <v>46387</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="54" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
+    <row r="3" spans="2:22" ht="54" x14ac:dyDescent="0.2">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C3" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="46">
+      <c r="F3" s="46">
         <v>151902</v>
       </c>
-      <c r="F2" s="46">
+      <c r="G3" s="46">
         <v>50727</v>
       </c>
-      <c r="G2" s="46">
+      <c r="H3" s="46">
         <v>175830</v>
       </c>
-      <c r="H2" s="46">
+      <c r="I3" s="46">
         <v>172017</v>
       </c>
-      <c r="I2" s="46">
+      <c r="J3" s="46">
         <v>210289</v>
       </c>
-      <c r="J2" s="46">
+      <c r="K3" s="46">
         <v>169129</v>
       </c>
-      <c r="K2" s="46">
+      <c r="L3" s="46">
         <v>28845</v>
       </c>
-      <c r="L2" s="46">
+      <c r="M3" s="46">
         <v>39741</v>
       </c>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="57"/>
-    </row>
-    <row r="3" spans="1:21" ht="54" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="47" t="s">
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="56"/>
+    </row>
+    <row r="4" spans="2:22" ht="54" x14ac:dyDescent="0.2">
+      <c r="B4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="48">
+      <c r="F4" s="48">
         <v>5252</v>
       </c>
-      <c r="F3" s="48">
+      <c r="G4" s="48">
         <v>7084</v>
       </c>
-      <c r="G3" s="48">
+      <c r="H4" s="48">
         <v>7262</v>
       </c>
-      <c r="H3" s="48">
+      <c r="I4" s="48">
         <v>5243</v>
       </c>
-      <c r="I3" s="48">
+      <c r="J4" s="48">
         <v>4215</v>
       </c>
-      <c r="J3" s="48">
+      <c r="K4" s="48">
         <v>3141</v>
       </c>
-      <c r="K3" s="48">
+      <c r="L4" s="48">
         <v>1639</v>
-      </c>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="57"/>
-    </row>
-    <row r="4" spans="1:21" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="48">
-        <v>1505</v>
-      </c>
-      <c r="F4" s="48">
-        <v>1224</v>
-      </c>
-      <c r="G4" s="48">
-        <v>1970</v>
-      </c>
-      <c r="H4" s="48">
-        <v>1546</v>
-      </c>
-      <c r="I4" s="48">
-        <v>1667</v>
-      </c>
-      <c r="J4" s="48">
-        <v>1518</v>
-      </c>
-      <c r="K4" s="48">
-        <v>825</v>
-      </c>
-      <c r="L4" s="48">
-        <v>792</v>
       </c>
       <c r="M4" s="49"/>
       <c r="N4" s="49"/>
       <c r="O4" s="49"/>
       <c r="P4" s="49"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-    </row>
-    <row r="8" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C8" s="56" t="s">
+      <c r="Q4" s="49"/>
+      <c r="R4" s="56"/>
+    </row>
+    <row r="5" spans="2:22" ht="27" x14ac:dyDescent="0.2">
+      <c r="B5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="48">
+        <v>1505</v>
+      </c>
+      <c r="G5" s="48">
+        <v>1224</v>
+      </c>
+      <c r="H5" s="48">
+        <v>1970</v>
+      </c>
+      <c r="I5" s="48">
+        <v>1546</v>
+      </c>
+      <c r="J5" s="48">
+        <v>1667</v>
+      </c>
+      <c r="K5" s="48">
+        <v>1518</v>
+      </c>
+      <c r="L5" s="48">
+        <v>825</v>
+      </c>
+      <c r="M5" s="48">
+        <v>792</v>
+      </c>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+    </row>
+    <row r="9" spans="2:22" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D9" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="53"/>
-      <c r="G8" s="19" t="s">
+      <c r="H9" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="T8" s="56" t="s">
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="U9" s="55" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="54" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="T9" s="55" t="s">
+    <row r="10" spans="2:22" s="53" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="U10" s="54" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C10" s="76" t="s">
+    <row r="11" spans="2:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D11" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="61"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D10)),_xlfn.FORMULATEXT(D10),"")</f>
+      <c r="E11" s="59"/>
+      <c r="H11" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E11)),_xlfn.FORMULATEXT(E11),"")</f>
         <v/>
       </c>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-    </row>
-    <row r="11" spans="1:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C11" s="76" t="s">
+    </row>
+    <row r="12" spans="2:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D12" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D11)),_xlfn.FORMULATEXT(D11),"")</f>
+      <c r="E12" s="59"/>
+      <c r="H12" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E12)),_xlfn.FORMULATEXT(E12),"")</f>
         <v/>
       </c>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="T11" s="75" t="s">
+      <c r="U12" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="U11" s="54" t="s">
+      <c r="V12" s="53" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="U12" s="54" t="s">
+    <row r="13" spans="2:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="V13" s="53" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="F13" s="59"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="U13" s="54" t="s">
+    <row r="14" spans="2:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="57"/>
+      <c r="V14" s="53" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C14" s="60" t="s">
+    <row r="15" spans="2:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D15" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="61"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D14)),_xlfn.FORMULATEXT(D14),"")</f>
+      <c r="E15" s="59"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E15)),_xlfn.FORMULATEXT(E15),"")</f>
         <v/>
       </c>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="U14" s="54" t="s">
+      <c r="V15" s="53" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C15" s="60" t="s">
+    <row r="16" spans="2:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D16" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="61"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D15)),_xlfn.FORMULATEXT(D15),"")</f>
+      <c r="E16" s="59"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E16)),_xlfn.FORMULATEXT(E16),"")</f>
         <v/>
       </c>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-    </row>
-    <row r="16" spans="1:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C16" s="63"/>
-      <c r="D16" s="64"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-    </row>
-    <row r="17" spans="3:21" s="54" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C17" s="60" t="s">
+    </row>
+    <row r="17" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D17" s="61"/>
+      <c r="E17" s="62"/>
+      <c r="G17" s="60"/>
+    </row>
+    <row r="18" spans="4:22" s="53" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D18" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D17)),_xlfn.FORMULATEXT(D17),"")</f>
+      <c r="E18" s="63"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E18)),_xlfn.FORMULATEXT(E18),"")</f>
         <v/>
       </c>
-      <c r="T17" s="123" t="s">
+      <c r="U18" s="113" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C18" s="63"/>
-      <c r="D18" s="64"/>
-      <c r="F18" s="66"/>
-    </row>
-    <row r="19" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C19" s="63"/>
-      <c r="D19" s="64"/>
-      <c r="F19" s="66"/>
-      <c r="T19" s="75" t="s">
+    <row r="19" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D19" s="61"/>
+      <c r="E19" s="62"/>
+      <c r="G19" s="60"/>
+    </row>
+    <row r="20" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D20" s="61"/>
+      <c r="E20" s="62"/>
+      <c r="G20" s="60"/>
+      <c r="U20" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="U19" s="54" t="s">
+      <c r="V20" s="53" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C20" s="64" t="s">
+    <row r="21" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D21" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="64"/>
-      <c r="F20" s="66"/>
-      <c r="U20" s="54" t="s">
+      <c r="E21" s="62"/>
+      <c r="G21" s="60"/>
+      <c r="V21" s="53" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C21" s="67" t="s">
+    <row r="22" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D22" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D21)),_xlfn.FORMULATEXT(D21),"")</f>
+      <c r="E22" s="65"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E22)),_xlfn.FORMULATEXT(E22),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C22" s="67" t="s">
+    <row r="23" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D23" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D22)),_xlfn.FORMULATEXT(D22),"")</f>
+      <c r="E23" s="65"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E23)),_xlfn.FORMULATEXT(E23),"")</f>
         <v/>
       </c>
-      <c r="T22" s="75" t="s">
+      <c r="U23" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="U22" s="54" t="s">
+      <c r="V23" s="53" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C23" s="67" t="s">
+    <row r="24" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D24" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D23)),_xlfn.FORMULATEXT(D23),"")</f>
+      <c r="E24" s="65"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E24)),_xlfn.FORMULATEXT(E24),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C24" s="63"/>
-      <c r="D24" s="69"/>
-      <c r="F24" s="66"/>
-    </row>
-    <row r="25" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C25" s="64" t="s">
+    <row r="25" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D25" s="61"/>
+      <c r="E25" s="66"/>
+      <c r="G25" s="60"/>
+    </row>
+    <row r="26" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D26" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="F25" s="66"/>
-    </row>
-    <row r="26" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C26" s="67" t="s">
+      <c r="E26" s="66"/>
+      <c r="G26" s="60"/>
+    </row>
+    <row r="27" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D27" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="68"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D26)),_xlfn.FORMULATEXT(D26),"")</f>
+      <c r="E27" s="65"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E27)),_xlfn.FORMULATEXT(E27),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C27" s="67" t="s">
+    <row r="28" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D28" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="68"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D27)),_xlfn.FORMULATEXT(D27),"")</f>
+      <c r="E28" s="65"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E28)),_xlfn.FORMULATEXT(E28),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C28" s="67" t="s">
+    <row r="29" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D29" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="68"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D28)),_xlfn.FORMULATEXT(D28),"")</f>
+      <c r="E29" s="65"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E29)),_xlfn.FORMULATEXT(E29),"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C29" s="63"/>
-      <c r="D29" s="69"/>
-      <c r="F29" s="66"/>
-    </row>
-    <row r="30" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C30" s="64" t="s">
+    <row r="30" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D30" s="61"/>
+      <c r="E30" s="66"/>
+      <c r="G30" s="60"/>
+    </row>
+    <row r="31" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D31" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="F30" s="66"/>
-    </row>
-    <row r="31" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C31" s="67" t="s">
+      <c r="E31" s="66"/>
+      <c r="G31" s="60"/>
+    </row>
+    <row r="32" spans="4:22" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D32" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="68"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D31)),_xlfn.FORMULATEXT(D31),"")</f>
+      <c r="E32" s="65"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E32)),_xlfn.FORMULATEXT(E32),"")</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="3:21" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C32" s="67" t="s">
+    <row r="33" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D33" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="68"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D32)),_xlfn.FORMULATEXT(D32),"")</f>
+      <c r="E33" s="65"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E33)),_xlfn.FORMULATEXT(E33),"")</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C33" s="67" t="s">
+    <row r="34" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D34" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="68"/>
-      <c r="F33" s="66"/>
-      <c r="G33" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D33)),_xlfn.FORMULATEXT(D33),"")</f>
+      <c r="E34" s="65"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E34)),_xlfn.FORMULATEXT(E34),"")</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C34" s="63"/>
-      <c r="D34" s="69"/>
-      <c r="F34" s="66"/>
-    </row>
-    <row r="35" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C35" s="64" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="69"/>
-      <c r="F35" s="66"/>
-    </row>
-    <row r="36" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C36" s="70" t="s">
+    <row r="35" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D35" s="61"/>
+      <c r="E35" s="66"/>
+      <c r="G35" s="60"/>
+    </row>
+    <row r="36" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D36" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" s="66"/>
+      <c r="G36" s="60"/>
+    </row>
+    <row r="37" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D37" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="71"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D36)),_xlfn.FORMULATEXT(D36),"")</f>
+      <c r="E37" s="68"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E37)),_xlfn.FORMULATEXT(E37),"")</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C37" s="67" t="s">
+    <row r="38" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D38" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="72"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D37)),_xlfn.FORMULATEXT(D37),"")</f>
+      <c r="E38" s="69"/>
+      <c r="G38" s="60"/>
+      <c r="H38" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E38)),_xlfn.FORMULATEXT(E38),"")</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C38" s="63"/>
-      <c r="D38" s="69"/>
-      <c r="F38" s="66"/>
-    </row>
-    <row r="39" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C39" s="67" t="s">
+    <row r="39" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D39" s="61"/>
+      <c r="E39" s="66"/>
+      <c r="G39" s="60"/>
+    </row>
+    <row r="40" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D40" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="68"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D39)),_xlfn.FORMULATEXT(D39),"")</f>
+      <c r="E40" s="65"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E40)),_xlfn.FORMULATEXT(E40),"")</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C40" s="73" t="s">
+    <row r="41" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D41" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="D40" s="72"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D40)),_xlfn.FORMULATEXT(D40),"")</f>
+      <c r="E41" s="69"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E41)),_xlfn.FORMULATEXT(E41),"")</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C41" s="63"/>
-      <c r="D41" s="74"/>
-      <c r="F41" s="66"/>
-    </row>
-    <row r="42" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C42" s="67" t="s">
+    <row r="42" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D42" s="61"/>
+      <c r="E42" s="71"/>
+      <c r="G42" s="60"/>
+    </row>
+    <row r="43" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D43" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D42)),_xlfn.FORMULATEXT(D42),"")</f>
+      <c r="E43" s="65"/>
+      <c r="G43" s="60"/>
+      <c r="H43" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E43)),_xlfn.FORMULATEXT(E43),"")</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C43" s="73" t="s">
+    <row r="44" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D44" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="D43" s="72"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D43)),_xlfn.FORMULATEXT(D43),"")</f>
+      <c r="E44" s="69"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E44)),_xlfn.FORMULATEXT(E44),"")</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C44" s="63"/>
-      <c r="D44" s="74"/>
-      <c r="F44" s="66"/>
-    </row>
-    <row r="45" spans="3:7" s="54" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="63"/>
-      <c r="D45" s="69"/>
-      <c r="F45" s="66"/>
-    </row>
-    <row r="46" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C46" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="69"/>
-      <c r="F46" s="66"/>
-    </row>
-    <row r="47" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C47" s="67" t="s">
+    <row r="45" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D45" s="61"/>
+      <c r="E45" s="71"/>
+      <c r="G45" s="60"/>
+    </row>
+    <row r="46" spans="4:8" s="53" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D46" s="61"/>
+      <c r="E46" s="66"/>
+      <c r="G46" s="60"/>
+    </row>
+    <row r="47" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D47" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="E47" s="66"/>
+      <c r="G47" s="60"/>
+    </row>
+    <row r="48" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D48" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D47" s="68"/>
-      <c r="F47" s="66"/>
-      <c r="G47" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D47)),_xlfn.FORMULATEXT(D47),"")</f>
+      <c r="E48" s="65"/>
+      <c r="G48" s="60"/>
+      <c r="H48" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E48)),_xlfn.FORMULATEXT(E48),"")</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C48" s="67" t="s">
+    <row r="49" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D49" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="72"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D48)),_xlfn.FORMULATEXT(D48),"")</f>
+      <c r="E49" s="69"/>
+      <c r="G49" s="60"/>
+      <c r="H49" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E49)),_xlfn.FORMULATEXT(E49),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C49" s="63"/>
-      <c r="D49" s="69"/>
-      <c r="F49" s="66"/>
-    </row>
-    <row r="50" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C50" s="67" t="s">
+    <row r="50" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D50" s="61"/>
+      <c r="E50" s="66"/>
+      <c r="G50" s="60"/>
+    </row>
+    <row r="51" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D51" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D50" s="68"/>
-      <c r="F50" s="66"/>
-      <c r="G50" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D50)),_xlfn.FORMULATEXT(D50),"")</f>
+      <c r="E51" s="65"/>
+      <c r="G51" s="60"/>
+      <c r="H51" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E51)),_xlfn.FORMULATEXT(E51),"")</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C51" s="67" t="s">
+    <row r="52" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D52" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="D51" s="72"/>
-      <c r="F51" s="66"/>
-      <c r="G51" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D51)),_xlfn.FORMULATEXT(D51),"")</f>
+      <c r="E52" s="69"/>
+      <c r="G52" s="60"/>
+      <c r="H52" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E52)),_xlfn.FORMULATEXT(E52),"")</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="D52" s="69"/>
-      <c r="F52" s="66"/>
-    </row>
-    <row r="53" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C53" s="67" t="s">
+    <row r="53" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="E53" s="66"/>
+      <c r="G53" s="60"/>
+    </row>
+    <row r="54" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D54" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="D53" s="68"/>
-      <c r="F53" s="66"/>
-      <c r="G53" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D53)),_xlfn.FORMULATEXT(D53),"")</f>
+      <c r="E54" s="65"/>
+      <c r="G54" s="60"/>
+      <c r="H54" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E54)),_xlfn.FORMULATEXT(E54),"")</f>
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C54" s="73" t="s">
+    <row r="55" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D55" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="D54" s="72"/>
-      <c r="F54" s="66"/>
-      <c r="G54" s="58" t="str">
-        <f ca="1">IF(NOT(ISBLANK(D54)),_xlfn.FORMULATEXT(D54),"")</f>
+      <c r="E55" s="69"/>
+      <c r="G55" s="60"/>
+      <c r="H55" s="53" t="str">
+        <f ca="1">IF(NOT(ISBLANK(E55)),_xlfn.FORMULATEXT(E55),"")</f>
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:7" s="54" customFormat="1" ht="13.5" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:8" s="53" customFormat="1" ht="13.5" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation errorStyle="information" operator="greaterThan" showErrorMessage="1" errorTitle="Message SISB" error="Veuillez entrer un nombre positif entier" promptTitle="Message SISB" prompt="veuillez entrer un nombre entier" sqref="E4:L4 E2:P3" xr:uid="{A2B7FEED-18F0-4152-A24C-CA0BC5A6B90E}"/>
+    <dataValidation errorStyle="information" operator="greaterThan" showErrorMessage="1" errorTitle="Message SISB" error="Veuillez entrer un nombre positif entier" promptTitle="Message SISB" prompt="veuillez entrer un nombre entier" sqref="F5:M5 F3:Q4" xr:uid="{A2B7FEED-18F0-4152-A24C-CA0BC5A6B90E}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16252,7 +17589,7 @@
       <c r="P4" s="49"/>
     </row>
     <row r="8" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="55" t="s">
         <v>69</v>
       </c>
       <c r="F8" s="19" t="s">
@@ -16263,14 +17600,14 @@
       <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:16" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
     </row>
     <row r="10" spans="1:16" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="77">
+      <c r="D10" s="73">
         <f>COUNTIF(B2:B4,"ASAP")</f>
         <v>2</v>
       </c>
@@ -16280,10 +17617,10 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="77">
+      <c r="D11" s="73">
         <f>COUNTIF(B2:B4,"FDOC")</f>
         <v>1</v>
       </c>
@@ -16293,14 +17630,14 @@
       </c>
     </row>
     <row r="12" spans="1:16" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
     </row>
     <row r="13" spans="1:16" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C13" s="60" t="s">
+      <c r="C13" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="59">
         <f>MIN(E1:P1)</f>
         <v>46053</v>
       </c>
@@ -16310,10 +17647,10 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="59">
         <f>MAX(E1:P1)</f>
         <v>46387</v>
       </c>
@@ -16323,15 +17660,15 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C15" s="63"/>
-      <c r="D15" s="64"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="62"/>
       <c r="F15" s="20"/>
     </row>
     <row r="16" spans="1:16" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="65">
+      <c r="D16" s="63">
         <f>COUNT(E1:P1)</f>
         <v>12</v>
       </c>
@@ -16342,27 +17679,27 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C17" s="63"/>
-      <c r="D17" s="64"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="62"/>
       <c r="F17" s="20"/>
     </row>
     <row r="18" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C18" s="63"/>
-      <c r="D18" s="64"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="62"/>
       <c r="F18" s="20"/>
     </row>
     <row r="19" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C19" s="64" t="s">
+      <c r="C19" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="64"/>
+      <c r="D19" s="62"/>
       <c r="F19" s="20"/>
     </row>
     <row r="20" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="68">
+      <c r="D20" s="65">
         <f>_xlfn.AGGREGATE(9,0,PlageEntrees2026)</f>
         <v>998480</v>
       </c>
@@ -16372,10 +17709,10 @@
       </c>
     </row>
     <row r="21" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C21" s="67" t="s">
+      <c r="C21" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="68">
+      <c r="D21" s="65">
         <f>_xlfn.AGGREGATE(9,0,PlagePrets2026)</f>
         <v>33836</v>
       </c>
@@ -16385,10 +17722,10 @@
       </c>
     </row>
     <row r="22" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C22" s="67" t="s">
+      <c r="C22" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="68">
+      <c r="D22" s="65">
         <f>_xlfn.AGGREGATE(9,0,PlagesSollicitations2026)</f>
         <v>11047</v>
       </c>
@@ -16398,22 +17735,22 @@
       </c>
     </row>
     <row r="23" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C23" s="63"/>
-      <c r="D23" s="69"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="66"/>
       <c r="F23" s="20"/>
     </row>
     <row r="24" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="69"/>
+      <c r="D24" s="66"/>
       <c r="F24" s="20"/>
     </row>
     <row r="25" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="68">
+      <c r="D25" s="65">
         <f>_xlfn.AGGREGATE(1,0,PlageEntrees2026)</f>
         <v>124810</v>
       </c>
@@ -16423,10 +17760,10 @@
       </c>
     </row>
     <row r="26" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C26" s="67" t="s">
+      <c r="C26" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="68">
+      <c r="D26" s="65">
         <f>_xlfn.AGGREGATE(1,0,PlagePrets2026)</f>
         <v>4833.7142857142853</v>
       </c>
@@ -16436,10 +17773,10 @@
       </c>
     </row>
     <row r="27" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C27" s="67" t="s">
+      <c r="C27" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="68">
+      <c r="D27" s="65">
         <f>_xlfn.AGGREGATE(1,0,PlagesSollicitations2026)</f>
         <v>1380.875</v>
       </c>
@@ -16449,22 +17786,22 @@
       </c>
     </row>
     <row r="28" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C28" s="63"/>
-      <c r="D28" s="69"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="66"/>
       <c r="F28" s="20"/>
     </row>
     <row r="29" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C29" s="64" t="s">
+      <c r="C29" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="69"/>
+      <c r="D29" s="66"/>
       <c r="F29" s="20"/>
     </row>
     <row r="30" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C30" s="67" t="s">
+      <c r="C30" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="68">
+      <c r="D30" s="65">
         <f>_xlfn.AGGREGATE(12,0,PlageEntrees2026)</f>
         <v>160515.5</v>
       </c>
@@ -16474,10 +17811,10 @@
       </c>
     </row>
     <row r="31" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C31" s="67" t="s">
+      <c r="C31" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="68">
+      <c r="D31" s="65">
         <f>_xlfn.AGGREGATE(12,0,PlagePrets2026)</f>
         <v>5243</v>
       </c>
@@ -16487,10 +17824,10 @@
       </c>
     </row>
     <row r="32" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C32" s="67" t="s">
+      <c r="C32" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="68">
+      <c r="D32" s="65">
         <f>_xlfn.AGGREGATE(12,0,PlagesSollicitations2026)</f>
         <v>1511.5</v>
       </c>
@@ -16500,22 +17837,22 @@
       </c>
     </row>
     <row r="33" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C33" s="63"/>
-      <c r="D33" s="69"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="66"/>
       <c r="F33" s="20"/>
     </row>
     <row r="34" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C34" s="64" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="69"/>
+      <c r="C34" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="66"/>
       <c r="F34" s="20"/>
     </row>
     <row r="35" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C35" s="70" t="s">
+      <c r="C35" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="71">
+      <c r="D35" s="68">
         <f>_xlfn.AGGREGATE(4,0,PlageEntrees2026)</f>
         <v>210289</v>
       </c>
@@ -16525,10 +17862,10 @@
       </c>
     </row>
     <row r="36" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C36" s="67" t="s">
+      <c r="C36" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="72">
+      <c r="D36" s="69">
         <f>_xlfn.XLOOKUP(D35,PlageEntrees2026,PlageDates2026)</f>
         <v>46173</v>
       </c>
@@ -16538,15 +17875,15 @@
       </c>
     </row>
     <row r="37" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C37" s="63"/>
-      <c r="D37" s="69"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="66"/>
       <c r="F37" s="20"/>
     </row>
     <row r="38" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C38" s="67" t="s">
+      <c r="C38" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="68">
+      <c r="D38" s="65">
         <f>_xlfn.AGGREGATE(4,0,PlagePrets2026)</f>
         <v>7262</v>
       </c>
@@ -16556,10 +17893,10 @@
       </c>
     </row>
     <row r="39" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C39" s="73" t="s">
+      <c r="C39" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="72">
+      <c r="D39" s="69">
         <f>_xlfn.XLOOKUP(D38,PlagePrets2026,PlageDates2026)</f>
         <v>46112</v>
       </c>
@@ -16569,15 +17906,15 @@
       </c>
     </row>
     <row r="40" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C40" s="63"/>
-      <c r="D40" s="74"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="71"/>
       <c r="F40" s="20"/>
     </row>
     <row r="41" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C41" s="67" t="s">
+      <c r="C41" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="68">
+      <c r="D41" s="65">
         <f>_xlfn.AGGREGATE(4,0,PlagesSollicitations2026)</f>
         <v>1970</v>
       </c>
@@ -16587,10 +17924,10 @@
       </c>
     </row>
     <row r="42" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C42" s="73" t="s">
+      <c r="C42" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="D42" s="72">
+      <c r="D42" s="69">
         <f>_xlfn.XLOOKUP(D41,PlagesSollicitations2026,PlageDates2026)</f>
         <v>46112</v>
       </c>
@@ -16600,27 +17937,27 @@
       </c>
     </row>
     <row r="43" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C43" s="63"/>
-      <c r="D43" s="74"/>
+      <c r="C43" s="61"/>
+      <c r="D43" s="71"/>
       <c r="F43" s="20"/>
     </row>
     <row r="44" spans="3:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="63"/>
-      <c r="D44" s="69"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="66"/>
       <c r="F44" s="20"/>
     </row>
     <row r="45" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C45" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" s="69"/>
+      <c r="C45" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="66"/>
       <c r="F45" s="20"/>
     </row>
     <row r="46" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="71">
+      <c r="D46" s="68">
         <f>_xlfn.AGGREGATE(5,0,PlageEntrees2026)</f>
         <v>28845</v>
       </c>
@@ -16630,10 +17967,10 @@
       </c>
     </row>
     <row r="47" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C47" s="67" t="s">
+      <c r="C47" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="72">
+      <c r="D47" s="69">
         <f>_xlfn.XLOOKUP(D46,PlageEntrees2026,PlageDates2026)</f>
         <v>46234</v>
       </c>
@@ -16643,15 +17980,15 @@
       </c>
     </row>
     <row r="48" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C48" s="63"/>
-      <c r="D48" s="69"/>
+      <c r="C48" s="61"/>
+      <c r="D48" s="66"/>
       <c r="F48" s="20"/>
     </row>
     <row r="49" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C49" s="67" t="s">
+      <c r="C49" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D49" s="68">
+      <c r="D49" s="65">
         <f>_xlfn.AGGREGATE(5,0,PlagePrets2026)</f>
         <v>1639</v>
       </c>
@@ -16661,10 +17998,10 @@
       </c>
     </row>
     <row r="50" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C50" s="67" t="s">
+      <c r="C50" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="D50" s="72">
+      <c r="D50" s="69">
         <f>_xlfn.XLOOKUP(D49,PlagePrets2026,PlageDates2026)</f>
         <v>46234</v>
       </c>
@@ -16674,15 +18011,15 @@
       </c>
     </row>
     <row r="51" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C51" s="54"/>
-      <c r="D51" s="74"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="71"/>
       <c r="F51" s="20"/>
     </row>
     <row r="52" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C52" s="67" t="s">
+      <c r="C52" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="D52" s="68">
+      <c r="D52" s="65">
         <f>_xlfn.AGGREGATE(5,0,PlagesSollicitations2026)</f>
         <v>792</v>
       </c>
@@ -16692,10 +18029,10 @@
       </c>
     </row>
     <row r="53" spans="3:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C53" s="73" t="s">
+      <c r="C53" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="D53" s="72">
+      <c r="D53" s="69">
         <f>_xlfn.XLOOKUP(D52,PlagesSollicitations2026,PlageDates2026)</f>
         <v>46265</v>
       </c>
@@ -16778,146 +18115,138 @@
       </c>
     </row>
     <row r="3" spans="2:17" ht="54" x14ac:dyDescent="0.2">
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="88" t="s">
+      <c r="D3" s="81" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="92">
+      <c r="F3" s="85">
         <v>151902</v>
       </c>
-      <c r="G3" s="92">
+      <c r="G3" s="85">
         <v>50727</v>
       </c>
-      <c r="H3" s="92">
+      <c r="H3" s="85">
         <v>175830</v>
       </c>
-      <c r="I3" s="92">
+      <c r="I3" s="85">
         <v>172017</v>
       </c>
-      <c r="J3" s="92">
+      <c r="J3" s="85">
         <v>210289</v>
       </c>
-      <c r="K3" s="92">
+      <c r="K3" s="85">
         <v>169129</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="85">
         <v>28845</v>
       </c>
-      <c r="M3" s="92">
+      <c r="M3" s="85">
         <v>39741</v>
       </c>
-      <c r="N3" s="92"/>
-      <c r="O3" s="92"/>
-      <c r="P3" s="92"/>
-      <c r="Q3" s="93"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="86"/>
     </row>
     <row r="4" spans="2:17" ht="54" x14ac:dyDescent="0.2">
-      <c r="B4" s="89" t="s">
+      <c r="B4" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="90" t="s">
+      <c r="C4" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="91" t="s">
+      <c r="D4" s="84" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="94">
+      <c r="F4" s="87">
         <v>5252</v>
       </c>
-      <c r="G4" s="94">
+      <c r="G4" s="87">
         <v>7084</v>
       </c>
-      <c r="H4" s="94">
+      <c r="H4" s="87">
         <v>7262</v>
       </c>
-      <c r="I4" s="94">
+      <c r="I4" s="87">
         <v>5243</v>
       </c>
-      <c r="J4" s="94">
+      <c r="J4" s="87">
         <v>4215</v>
       </c>
-      <c r="K4" s="94">
+      <c r="K4" s="87">
         <v>3141</v>
       </c>
-      <c r="L4" s="94">
+      <c r="L4" s="87">
         <v>1639</v>
       </c>
-      <c r="M4" s="95"/>
-      <c r="N4" s="95"/>
-      <c r="O4" s="95"/>
-      <c r="P4" s="95"/>
-      <c r="Q4" s="96"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="89"/>
     </row>
     <row r="5" spans="2:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="90" t="s">
+      <c r="C5" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="91" t="s">
+      <c r="D5" s="84" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="94">
+      <c r="F5" s="87">
         <v>1505</v>
       </c>
-      <c r="G5" s="94">
+      <c r="G5" s="87">
         <v>1224</v>
       </c>
-      <c r="H5" s="94">
+      <c r="H5" s="87">
         <v>1970</v>
       </c>
-      <c r="I5" s="94">
+      <c r="I5" s="87">
         <v>1546</v>
       </c>
-      <c r="J5" s="94">
+      <c r="J5" s="87">
         <v>1667</v>
       </c>
-      <c r="K5" s="94">
+      <c r="K5" s="87">
         <v>1518</v>
       </c>
-      <c r="L5" s="94">
+      <c r="L5" s="87">
         <v>825</v>
       </c>
-      <c r="M5" s="94">
+      <c r="M5" s="87">
         <v>792</v>
       </c>
-      <c r="N5" s="95"/>
-      <c r="O5" s="95"/>
-      <c r="P5" s="95"/>
-      <c r="Q5" s="96"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="88"/>
+      <c r="P5" s="88"/>
+      <c r="Q5" s="89"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="C8" s="78"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="78"/>
-      <c r="J8" s="78"/>
+      <c r="G8" s="74"/>
     </row>
     <row r="9" spans="2:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="99"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
       <c r="G9" s="19" t="s">
         <v>61</v>
       </c>
@@ -16926,16 +18255,14 @@
       <c r="J9" s="14"/>
     </row>
     <row r="10" spans="2:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C10" s="78"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
     </row>
     <row r="11" spans="2:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C11" s="78"/>
-      <c r="D11" s="76" t="s">
+      <c r="D11" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="77">
+      <c r="E11" s="73">
         <f>COUNTIF(C3:C5,"ASAP")</f>
         <v>2</v>
       </c>
@@ -16945,11 +18272,10 @@
       </c>
     </row>
     <row r="12" spans="2:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C12" s="78"/>
-      <c r="D12" s="76" t="s">
+      <c r="D12" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="77">
+      <c r="E12" s="73">
         <f>COUNTIF(C3:C5,"FDOC")</f>
         <v>1</v>
       </c>
@@ -16959,16 +18285,14 @@
       </c>
     </row>
     <row r="13" spans="2:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C13" s="78"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
     </row>
     <row r="14" spans="2:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C14" s="78"/>
-      <c r="D14" s="60" t="s">
+      <c r="D14" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="59">
         <f>MIN(F2:Q2)</f>
         <v>46053</v>
       </c>
@@ -16978,11 +18302,10 @@
       </c>
     </row>
     <row r="15" spans="2:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C15" s="78"/>
-      <c r="D15" s="60" t="s">
+      <c r="D15" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="59">
         <f>MAX(F2:Q2)</f>
         <v>46387</v>
       </c>
@@ -16992,17 +18315,15 @@
       </c>
     </row>
     <row r="16" spans="2:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C16" s="78"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="64"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="62"/>
       <c r="G16" s="20"/>
     </row>
-    <row r="17" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C17" s="78"/>
-      <c r="D17" s="60" t="s">
+    <row r="17" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D17" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="63">
         <f>COUNT(F2:Q2)</f>
         <v>12</v>
       </c>
@@ -17012,32 +18333,28 @@
       </c>
       <c r="H17" s="15"/>
     </row>
-    <row r="18" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C18" s="78"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="64"/>
+    <row r="18" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D18" s="61"/>
+      <c r="E18" s="62"/>
       <c r="G18" s="20"/>
     </row>
-    <row r="19" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C19" s="78"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="64"/>
+    <row r="19" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D19" s="61"/>
+      <c r="E19" s="62"/>
       <c r="G19" s="20"/>
     </row>
-    <row r="20" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C20" s="78"/>
-      <c r="D20" s="64" t="s">
+    <row r="20" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D20" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="64"/>
+      <c r="E20" s="62"/>
       <c r="G20" s="20"/>
     </row>
-    <row r="21" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C21" s="78"/>
-      <c r="D21" s="67" t="s">
+    <row r="21" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D21" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="68">
+      <c r="E21" s="65">
         <f>_xlfn.AGGREGATE(9,0,PlageEntrees2026)</f>
         <v>998480</v>
       </c>
@@ -17046,12 +18363,11 @@
         <v>=AGREGAT(9;0;PlageEntrees2026)</v>
       </c>
     </row>
-    <row r="22" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C22" s="78"/>
-      <c r="D22" s="67" t="s">
+    <row r="22" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D22" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="68">
+      <c r="E22" s="65">
         <f>_xlfn.AGGREGATE(9,0,PlagePrets2026)</f>
         <v>33836</v>
       </c>
@@ -17060,12 +18376,11 @@
         <v>=AGREGAT(9;0;PlagePrets2026)</v>
       </c>
     </row>
-    <row r="23" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C23" s="78"/>
-      <c r="D23" s="67" t="s">
+    <row r="23" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D23" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="68">
+      <c r="E23" s="65">
         <f>_xlfn.AGGREGATE(9,0,PlagesSollicitations2026)</f>
         <v>11047</v>
       </c>
@@ -17074,26 +18389,23 @@
         <v>=AGREGAT(9;0;PlagesSollicitations2026)</v>
       </c>
     </row>
-    <row r="24" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C24" s="78"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="69"/>
+    <row r="24" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D24" s="61"/>
+      <c r="E24" s="66"/>
       <c r="G24" s="20"/>
     </row>
-    <row r="25" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C25" s="78"/>
-      <c r="D25" s="64" t="s">
+    <row r="25" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D25" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="E25" s="69"/>
+      <c r="E25" s="66"/>
       <c r="G25" s="20"/>
     </row>
-    <row r="26" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C26" s="78"/>
-      <c r="D26" s="67" t="s">
+    <row r="26" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D26" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="68">
+      <c r="E26" s="65">
         <f>_xlfn.AGGREGATE(1,0,PlageEntrees2026)</f>
         <v>124810</v>
       </c>
@@ -17102,12 +18414,11 @@
         <v>=AGREGAT(1;0;PlageEntrees2026)</v>
       </c>
     </row>
-    <row r="27" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C27" s="78"/>
-      <c r="D27" s="67" t="s">
+    <row r="27" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D27" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="68">
+      <c r="E27" s="65">
         <f>_xlfn.AGGREGATE(1,0,PlagePrets2026)</f>
         <v>4833.7142857142853</v>
       </c>
@@ -17116,12 +18427,11 @@
         <v>=AGREGAT(1;0;PlagePrets2026)</v>
       </c>
     </row>
-    <row r="28" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C28" s="78"/>
-      <c r="D28" s="67" t="s">
+    <row r="28" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D28" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="68">
+      <c r="E28" s="65">
         <f>_xlfn.AGGREGATE(1,0,PlagesSollicitations2026)</f>
         <v>1380.875</v>
       </c>
@@ -17130,26 +18440,23 @@
         <v>=AGREGAT(1;0;PlagesSollicitations2026)</v>
       </c>
     </row>
-    <row r="29" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C29" s="78"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="69"/>
+    <row r="29" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D29" s="61"/>
+      <c r="E29" s="66"/>
       <c r="G29" s="20"/>
     </row>
-    <row r="30" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C30" s="78"/>
-      <c r="D30" s="64" t="s">
+    <row r="30" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D30" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="69"/>
+      <c r="E30" s="66"/>
       <c r="G30" s="20"/>
     </row>
-    <row r="31" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C31" s="78"/>
-      <c r="D31" s="67" t="s">
+    <row r="31" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D31" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="E31" s="68">
+      <c r="E31" s="65">
         <f>_xlfn.AGGREGATE(12,0,PlageEntrees2026)</f>
         <v>160515.5</v>
       </c>
@@ -17158,12 +18465,11 @@
         <v>=AGREGAT(12;0;PlageEntrees2026)</v>
       </c>
     </row>
-    <row r="32" spans="3:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C32" s="78"/>
-      <c r="D32" s="67" t="s">
+    <row r="32" spans="4:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D32" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="68">
+      <c r="E32" s="65">
         <f>_xlfn.AGGREGATE(12,0,PlagePrets2026)</f>
         <v>5243</v>
       </c>
@@ -17172,12 +18478,11 @@
         <v>=AGREGAT(12;0;PlagePrets2026)</v>
       </c>
     </row>
-    <row r="33" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C33" s="78"/>
-      <c r="D33" s="67" t="s">
+    <row r="33" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D33" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="68">
+      <c r="E33" s="65">
         <f>_xlfn.AGGREGATE(12,0,PlagesSollicitations2026)</f>
         <v>1511.5</v>
       </c>
@@ -17186,26 +18491,23 @@
         <v>=AGREGAT(12;0;PlagesSollicitations2026)</v>
       </c>
     </row>
-    <row r="34" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C34" s="78"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="69"/>
+    <row r="34" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D34" s="61"/>
+      <c r="E34" s="66"/>
       <c r="G34" s="20"/>
     </row>
-    <row r="35" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C35" s="78"/>
-      <c r="D35" s="64" t="s">
+    <row r="35" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D35" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="69"/>
+      <c r="E35" s="66"/>
       <c r="G35" s="20"/>
     </row>
-    <row r="36" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C36" s="78"/>
-      <c r="D36" s="70" t="s">
+    <row r="36" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D36" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="71">
+      <c r="E36" s="68">
         <f>_xlfn.AGGREGATE(4,0,PlageEntrees2026)</f>
         <v>210289</v>
       </c>
@@ -17214,12 +18516,11 @@
         <v>=AGREGAT(4;0;PlageEntrees2026)</v>
       </c>
     </row>
-    <row r="37" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C37" s="78"/>
-      <c r="D37" s="67" t="s">
+    <row r="37" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D37" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="72">
+      <c r="E37" s="69">
         <f>_xlfn.XLOOKUP(E36,PlageEntrees2026,PlageDates2026)</f>
         <v>46173</v>
       </c>
@@ -17228,18 +18529,16 @@
         <v>=RECHERCHEX(E36;PlageEntrees2026;PlageDates2026)</v>
       </c>
     </row>
-    <row r="38" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C38" s="78"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="69"/>
+    <row r="38" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D38" s="61"/>
+      <c r="E38" s="66"/>
       <c r="G38" s="20"/>
     </row>
-    <row r="39" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C39" s="78"/>
-      <c r="D39" s="67" t="s">
+    <row r="39" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D39" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="E39" s="68">
+      <c r="E39" s="65">
         <f>_xlfn.AGGREGATE(4,0,PlagePrets2026)</f>
         <v>7262</v>
       </c>
@@ -17248,12 +18547,11 @@
         <v>=AGREGAT(4;0;PlagePrets2026)</v>
       </c>
     </row>
-    <row r="40" spans="3:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="78"/>
-      <c r="D40" s="73" t="s">
+    <row r="40" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="72">
+      <c r="E40" s="69">
         <f>_xlfn.XLOOKUP(E39,PlagePrets2026,PlageDates2026)</f>
         <v>46112</v>
       </c>
@@ -17262,18 +18560,16 @@
         <v>=RECHERCHEX(E39;PlagePrets2026;PlageDates2026)</v>
       </c>
     </row>
-    <row r="41" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C41" s="78"/>
-      <c r="D41" s="63"/>
-      <c r="E41" s="74"/>
+    <row r="41" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D41" s="61"/>
+      <c r="E41" s="71"/>
       <c r="G41" s="20"/>
     </row>
-    <row r="42" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C42" s="78"/>
-      <c r="D42" s="67" t="s">
+    <row r="42" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D42" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="68">
+      <c r="E42" s="65">
         <f>_xlfn.AGGREGATE(4,0,PlagesSollicitations2026)</f>
         <v>1970</v>
       </c>
@@ -17282,12 +18578,11 @@
         <v>=AGREGAT(4;0;PlagesSollicitations2026)</v>
       </c>
     </row>
-    <row r="43" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C43" s="78"/>
-      <c r="D43" s="73" t="s">
+    <row r="43" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D43" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="E43" s="72">
+      <c r="E43" s="69">
         <f>_xlfn.XLOOKUP(E42,PlagesSollicitations2026,PlageDates2026)</f>
         <v>46112</v>
       </c>
@@ -17296,32 +18591,28 @@
         <v>=RECHERCHEX(E42;PlagesSollicitations2026;PlageDates2026)</v>
       </c>
     </row>
-    <row r="44" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C44" s="78"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="74"/>
+    <row r="44" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D44" s="61"/>
+      <c r="E44" s="71"/>
       <c r="G44" s="20"/>
     </row>
-    <row r="45" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C45" s="78"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="69"/>
+    <row r="45" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D45" s="61"/>
+      <c r="E45" s="66"/>
       <c r="G45" s="20"/>
     </row>
-    <row r="46" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C46" s="78"/>
-      <c r="D46" s="64" t="s">
+    <row r="46" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D46" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="E46" s="69"/>
+      <c r="E46" s="66"/>
       <c r="G46" s="20"/>
     </row>
-    <row r="47" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C47" s="78"/>
-      <c r="D47" s="67" t="s">
+    <row r="47" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D47" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E47" s="71">
+      <c r="E47" s="68">
         <f>_xlfn.AGGREGATE(5,0,PlageEntrees2026)</f>
         <v>28845</v>
       </c>
@@ -17330,12 +18621,11 @@
         <v>=AGREGAT(5;0;PlageEntrees2026)</v>
       </c>
     </row>
-    <row r="48" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C48" s="78"/>
-      <c r="D48" s="67" t="s">
+    <row r="48" spans="4:7" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D48" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="E48" s="72">
+      <c r="E48" s="69">
         <f>_xlfn.XLOOKUP(E47,PlageEntrees2026,PlageDates2026)</f>
         <v>46234</v>
       </c>
@@ -17345,16 +18635,15 @@
       </c>
     </row>
     <row r="49" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="C49" s="78"/>
-      <c r="D49" s="63"/>
-      <c r="E49" s="69"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="66"/>
       <c r="G49" s="20"/>
     </row>
     <row r="50" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="D50" s="67" t="s">
+      <c r="D50" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="E50" s="68">
+      <c r="E50" s="65">
         <f>_xlfn.AGGREGATE(5,0,PlagePrets2026)</f>
         <v>1639</v>
       </c>
@@ -17364,10 +18653,10 @@
       </c>
     </row>
     <row r="51" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="D51" s="67" t="s">
+      <c r="D51" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="E51" s="72">
+      <c r="E51" s="69">
         <f>_xlfn.XLOOKUP(E50,PlagePrets2026,PlageDates2026)</f>
         <v>46234</v>
       </c>
@@ -17377,15 +18666,15 @@
       </c>
     </row>
     <row r="52" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="D52" s="54"/>
-      <c r="E52" s="74"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="71"/>
       <c r="G52" s="20"/>
     </row>
     <row r="53" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="D53" s="67" t="s">
+      <c r="D53" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="E53" s="68">
+      <c r="E53" s="65">
         <f>_xlfn.AGGREGATE(5,0,PlagesSollicitations2026)</f>
         <v>792</v>
       </c>
@@ -17395,10 +18684,10 @@
       </c>
     </row>
     <row r="54" spans="3:7" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="D54" s="73" t="s">
+      <c r="D54" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="E54" s="72">
+      <c r="E54" s="69">
         <f>_xlfn.XLOOKUP(E53,PlagesSollicitations2026,PlageDates2026)</f>
         <v>46265</v>
       </c>
@@ -17408,15 +18697,15 @@
       </c>
     </row>
     <row r="58" spans="3:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C58" s="97" t="s">
+      <c r="C58" s="90" t="s">
         <v>74</v>
       </c>
-      <c r="D58" s="98"/>
-      <c r="E58" s="98"/>
-      <c r="F58" s="98"/>
+      <c r="D58" s="91"/>
+      <c r="E58" s="91"/>
+      <c r="F58" s="91"/>
     </row>
     <row r="92" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D92" s="100" t="s">
+      <c r="D92" s="74" t="s">
         <v>76</v>
       </c>
     </row>
@@ -17426,16 +18715,16 @@
       </c>
     </row>
     <row r="95" spans="4:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="D95" s="101" t="s">
+      <c r="D95" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="E95" s="102">
+      <c r="E95" s="93">
         <f>CORREL(F3:Q3,F5:Q5)</f>
         <v>0.90035192229648831</v>
       </c>
     </row>
     <row r="98" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D98" s="100" t="s">
+      <c r="D98" s="74" t="s">
         <v>78</v>
       </c>
     </row>
@@ -17445,10 +18734,10 @@
       </c>
     </row>
     <row r="101" spans="4:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="D101" s="101" t="s">
+      <c r="D101" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="E101" s="102">
+      <c r="E101" s="93">
         <f>RSQ(F3:Q3,F5:Q5)</f>
         <v>0.81063358398298213</v>
       </c>
@@ -17528,7 +18817,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B2:AG60"/>
+  <dimension ref="B2:AG54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.6640625" customWidth="1"/>
@@ -17545,13 +18834,12 @@
     <col min="13" max="13" width="14.83203125" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
     <col min="16" max="17" width="13.83203125" customWidth="1"/>
-    <col min="18" max="18" width="4.6640625" style="78" customWidth="1"/>
+    <col min="18" max="18" width="4.6640625" customWidth="1"/>
     <col min="19" max="19" width="11.1640625" customWidth="1"/>
     <col min="21" max="21" width="59.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.5" customWidth="1"/>
     <col min="23" max="23" width="15.1640625" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
-    <col min="25" max="27" width="18" style="99" customWidth="1"/>
+    <col min="24" max="27" width="18" customWidth="1"/>
     <col min="29" max="29" width="74.33203125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="13.33203125" customWidth="1"/>
     <col min="31" max="31" width="18.33203125" customWidth="1"/>
@@ -17561,20 +18849,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="112" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AC3" s="56" t="s">
+      <c r="AC3" s="55" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="U5" s="56" t="s">
+      <c r="U5" s="55" t="s">
         <v>84</v>
       </c>
       <c r="AC5" s="37" t="s">
@@ -17585,7 +18873,7 @@
       </c>
     </row>
     <row r="6" spans="2:33" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="AA6" s="114"/>
+      <c r="AA6" s="104"/>
     </row>
     <row r="7" spans="2:33" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="27" t="s">
@@ -17636,8 +18924,8 @@
       <c r="Q7" s="29">
         <v>46387</v>
       </c>
-      <c r="R7" s="119"/>
-      <c r="S7" s="109" t="s">
+      <c r="R7" s="109"/>
+      <c r="S7" s="99" t="s">
         <v>81</v>
       </c>
       <c r="T7" s="31"/>
@@ -17653,8 +18941,8 @@
       <c r="X7" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="Y7" s="114"/>
-      <c r="Z7" s="114"/>
+      <c r="Y7" s="104"/>
+      <c r="Z7" s="104"/>
       <c r="AC7" s="37" t="s">
         <v>68</v>
       </c>
@@ -17684,36 +18972,36 @@
       <c r="E8" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="104">
+      <c r="F8" s="94">
         <v>151902</v>
       </c>
-      <c r="G8" s="104">
+      <c r="G8" s="94">
         <v>50727</v>
       </c>
-      <c r="H8" s="104">
+      <c r="H8" s="94">
         <v>175830</v>
       </c>
-      <c r="I8" s="104">
+      <c r="I8" s="94">
         <v>172017</v>
       </c>
-      <c r="J8" s="104">
+      <c r="J8" s="94">
         <v>210289</v>
       </c>
-      <c r="K8" s="104">
+      <c r="K8" s="94">
         <v>169129</v>
       </c>
-      <c r="L8" s="104">
+      <c r="L8" s="94">
         <v>28845</v>
       </c>
-      <c r="M8" s="104">
+      <c r="M8" s="94">
         <v>39741</v>
       </c>
-      <c r="N8" s="104"/>
-      <c r="O8" s="104"/>
-      <c r="P8" s="104"/>
-      <c r="Q8" s="105"/>
-      <c r="R8" s="118"/>
-      <c r="S8" s="116">
+      <c r="N8" s="94"/>
+      <c r="O8" s="94"/>
+      <c r="P8" s="94"/>
+      <c r="Q8" s="95"/>
+      <c r="R8" s="108"/>
+      <c r="S8" s="106">
         <f>SUM(F8:Q8)</f>
         <v>998480</v>
       </c>
@@ -17729,16 +19017,16 @@
       <c r="X8" s="41">
         <v>151902</v>
       </c>
-      <c r="Y8" s="115"/>
-      <c r="Z8" s="115"/>
-      <c r="AA8" s="115"/>
+      <c r="Y8" s="105"/>
+      <c r="Z8" s="105"/>
+      <c r="AA8" s="105"/>
       <c r="AC8" s="40" t="s">
         <v>4</v>
       </c>
       <c r="AD8" s="38">
         <v>998480</v>
       </c>
-      <c r="AE8" s="121">
+      <c r="AE8" s="111">
         <v>998480</v>
       </c>
       <c r="AF8" s="39">
@@ -17759,34 +19047,34 @@
       <c r="E9" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="106">
+      <c r="F9" s="96">
         <v>5252</v>
       </c>
-      <c r="G9" s="106">
+      <c r="G9" s="96">
         <v>7084</v>
       </c>
-      <c r="H9" s="106">
+      <c r="H9" s="96">
         <v>7262</v>
       </c>
-      <c r="I9" s="106">
+      <c r="I9" s="96">
         <v>5243</v>
       </c>
-      <c r="J9" s="106">
+      <c r="J9" s="96">
         <v>4215</v>
       </c>
-      <c r="K9" s="106">
+      <c r="K9" s="96">
         <v>3141</v>
       </c>
-      <c r="L9" s="106">
+      <c r="L9" s="96">
         <v>1639</v>
       </c>
-      <c r="M9" s="107"/>
-      <c r="N9" s="107"/>
-      <c r="O9" s="107"/>
-      <c r="P9" s="107"/>
-      <c r="Q9" s="108"/>
-      <c r="R9" s="120"/>
-      <c r="S9" s="117">
+      <c r="M9" s="97"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="97"/>
+      <c r="P9" s="97"/>
+      <c r="Q9" s="98"/>
+      <c r="R9" s="110"/>
+      <c r="S9" s="107">
         <f>SUM(F9:Q9)</f>
         <v>33836</v>
       </c>
@@ -17802,16 +19090,16 @@
       <c r="X9" s="42">
         <v>50727</v>
       </c>
-      <c r="Y9" s="115"/>
-      <c r="Z9" s="115"/>
-      <c r="AA9" s="115"/>
+      <c r="Y9" s="105"/>
+      <c r="Z9" s="105"/>
+      <c r="AA9" s="105"/>
       <c r="AC9" s="44">
         <v>46053</v>
       </c>
       <c r="AD9" s="38">
         <v>151902</v>
       </c>
-      <c r="AE9" s="103">
+      <c r="AE9">
         <v>151902</v>
       </c>
       <c r="AF9" s="39">
@@ -17832,36 +19120,36 @@
       <c r="E10" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="106">
+      <c r="F10" s="96">
         <v>1505</v>
       </c>
-      <c r="G10" s="106">
+      <c r="G10" s="96">
         <v>1224</v>
       </c>
-      <c r="H10" s="106">
+      <c r="H10" s="96">
         <v>1970</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="96">
         <v>1546</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="96">
         <v>1667</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="96">
         <v>1518</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="96">
         <v>825</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="96">
         <v>792</v>
       </c>
-      <c r="N10" s="107"/>
-      <c r="O10" s="107"/>
-      <c r="P10" s="107"/>
-      <c r="Q10" s="108"/>
-      <c r="R10" s="120"/>
-      <c r="S10" s="117">
+      <c r="N10" s="97"/>
+      <c r="O10" s="97"/>
+      <c r="P10" s="97"/>
+      <c r="Q10" s="98"/>
+      <c r="R10" s="110"/>
+      <c r="S10" s="107">
         <f>SUM(F10:Q10)</f>
         <v>11047</v>
       </c>
@@ -17877,16 +19165,16 @@
       <c r="X10" s="42">
         <v>175830</v>
       </c>
-      <c r="Y10" s="115"/>
-      <c r="Z10" s="115"/>
-      <c r="AA10" s="115"/>
+      <c r="Y10" s="105"/>
+      <c r="Z10" s="105"/>
+      <c r="AA10" s="105"/>
       <c r="AC10" s="44">
         <v>46081</v>
       </c>
       <c r="AD10" s="38">
         <v>50727</v>
       </c>
-      <c r="AE10" s="103">
+      <c r="AE10">
         <v>50727</v>
       </c>
       <c r="AF10" s="39">
@@ -17909,16 +19197,16 @@
       <c r="X11" s="42">
         <v>172017</v>
       </c>
-      <c r="Y11" s="115"/>
-      <c r="Z11" s="115"/>
-      <c r="AA11" s="115"/>
+      <c r="Y11" s="105"/>
+      <c r="Z11" s="105"/>
+      <c r="AA11" s="105"/>
       <c r="AC11" s="44">
         <v>46112</v>
       </c>
       <c r="AD11" s="38">
         <v>175830</v>
       </c>
-      <c r="AE11" s="103">
+      <c r="AE11">
         <v>175830</v>
       </c>
       <c r="AF11" s="39">
@@ -17941,16 +19229,16 @@
       <c r="X12" s="42">
         <v>210289</v>
       </c>
-      <c r="Y12" s="115"/>
-      <c r="Z12" s="115"/>
-      <c r="AA12" s="115"/>
+      <c r="Y12" s="105"/>
+      <c r="Z12" s="105"/>
+      <c r="AA12" s="105"/>
       <c r="AC12" s="44">
         <v>46142</v>
       </c>
       <c r="AD12" s="38">
         <v>172017</v>
       </c>
-      <c r="AE12" s="103">
+      <c r="AE12">
         <v>172017</v>
       </c>
       <c r="AF12" s="39">
@@ -17961,16 +19249,7 @@
       </c>
     </row>
     <row r="13" spans="2:33" ht="12" x14ac:dyDescent="0.2">
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
+      <c r="G13" s="74"/>
       <c r="U13" s="35" t="s">
         <v>4</v>
       </c>
@@ -17983,16 +19262,16 @@
       <c r="X13" s="42">
         <v>169129</v>
       </c>
-      <c r="Y13" s="115"/>
-      <c r="Z13" s="115"/>
-      <c r="AA13" s="115"/>
+      <c r="Y13" s="105"/>
+      <c r="Z13" s="105"/>
+      <c r="AA13" s="105"/>
       <c r="AC13" s="44">
         <v>46173</v>
       </c>
       <c r="AD13" s="38">
         <v>210289</v>
       </c>
-      <c r="AE13" s="103">
+      <c r="AE13">
         <v>210289</v>
       </c>
       <c r="AF13" s="39">
@@ -18003,16 +19282,9 @@
       </c>
     </row>
     <row r="14" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="78"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="76"/>
+      <c r="G14" s="20"/>
       <c r="U14" s="35" t="s">
         <v>4</v>
       </c>
@@ -18025,16 +19297,16 @@
       <c r="X14" s="42">
         <v>28845</v>
       </c>
-      <c r="Y14" s="115"/>
-      <c r="Z14" s="115"/>
-      <c r="AA14" s="115"/>
+      <c r="Y14" s="105"/>
+      <c r="Z14" s="105"/>
+      <c r="AA14" s="105"/>
       <c r="AC14" s="44">
         <v>46203</v>
       </c>
       <c r="AD14" s="38">
         <v>169129</v>
       </c>
-      <c r="AE14" s="103">
+      <c r="AE14">
         <v>169129</v>
       </c>
       <c r="AF14" s="39">
@@ -18045,16 +19317,9 @@
       </c>
     </row>
     <row r="15" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="78"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="76"/>
+      <c r="G15" s="20"/>
       <c r="U15" s="35" t="s">
         <v>4</v>
       </c>
@@ -18067,16 +19332,16 @@
       <c r="X15" s="42">
         <v>39741</v>
       </c>
-      <c r="Y15" s="115"/>
-      <c r="Z15" s="115"/>
-      <c r="AA15" s="115"/>
+      <c r="Y15" s="105"/>
+      <c r="Z15" s="105"/>
+      <c r="AA15" s="105"/>
       <c r="AC15" s="44">
         <v>46234</v>
       </c>
       <c r="AD15" s="38">
         <v>28845</v>
       </c>
-      <c r="AE15" s="103">
+      <c r="AE15">
         <v>28845</v>
       </c>
       <c r="AF15" s="39">
@@ -18087,13 +19352,7 @@
       </c>
     </row>
     <row r="16" spans="2:33" ht="12" x14ac:dyDescent="0.2">
-      <c r="F16" s="78"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78"/>
+      <c r="G16" s="20"/>
       <c r="U16" s="35" t="s">
         <v>4</v>
       </c>
@@ -18106,16 +19365,16 @@
       <c r="X16" s="42">
         <v>0</v>
       </c>
-      <c r="Y16" s="115"/>
-      <c r="Z16" s="115"/>
-      <c r="AA16" s="115"/>
+      <c r="Y16" s="105"/>
+      <c r="Z16" s="105"/>
+      <c r="AA16" s="105"/>
       <c r="AC16" s="44">
         <v>46265</v>
       </c>
       <c r="AD16" s="38">
         <v>39741</v>
       </c>
-      <c r="AE16" s="103">
+      <c r="AE16">
         <v>39741</v>
       </c>
       <c r="AF16" s="39">
@@ -18126,13 +19385,8 @@
       </c>
     </row>
     <row r="17" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F17" s="78"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="15"/>
       <c r="U17" s="35" t="s">
         <v>4</v>
       </c>
@@ -18145,16 +19399,16 @@
       <c r="X17" s="42">
         <v>0</v>
       </c>
-      <c r="Y17" s="115"/>
-      <c r="Z17" s="115"/>
-      <c r="AA17" s="115"/>
+      <c r="Y17" s="105"/>
+      <c r="Z17" s="105"/>
+      <c r="AA17" s="105"/>
       <c r="AC17" s="44">
         <v>46295</v>
       </c>
       <c r="AD17" s="38">
         <v>0</v>
       </c>
-      <c r="AE17" s="103">
+      <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17" s="39">
@@ -18165,10 +19419,6 @@
       </c>
     </row>
     <row r="18" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
       <c r="U18" s="35" t="s">
         <v>4</v>
       </c>
@@ -18181,16 +19431,16 @@
       <c r="X18" s="42">
         <v>0</v>
       </c>
-      <c r="Y18" s="115"/>
-      <c r="Z18" s="115"/>
-      <c r="AA18" s="115"/>
+      <c r="Y18" s="105"/>
+      <c r="Z18" s="105"/>
+      <c r="AA18" s="105"/>
       <c r="AC18" s="44">
         <v>46326</v>
       </c>
       <c r="AD18" s="38">
         <v>0</v>
       </c>
-      <c r="AE18" s="103">
+      <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18" s="39">
@@ -18201,10 +19451,6 @@
       </c>
     </row>
     <row r="19" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="78"/>
       <c r="U19" s="35" t="s">
         <v>4</v>
       </c>
@@ -18217,16 +19463,16 @@
       <c r="X19" s="42">
         <v>0</v>
       </c>
-      <c r="Y19" s="115"/>
-      <c r="Z19" s="115"/>
-      <c r="AA19" s="115"/>
+      <c r="Y19" s="105"/>
+      <c r="Z19" s="105"/>
+      <c r="AA19" s="105"/>
       <c r="AC19" s="44">
         <v>46356</v>
       </c>
       <c r="AD19" s="38">
         <v>0</v>
       </c>
-      <c r="AE19" s="103">
+      <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19" s="39">
@@ -18237,13 +19483,9 @@
       </c>
     </row>
     <row r="20" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="I20" s="78"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
       <c r="U20" s="35" t="s">
         <v>33</v>
       </c>
@@ -18256,16 +19498,16 @@
       <c r="X20" s="42">
         <v>5252</v>
       </c>
-      <c r="Y20" s="115"/>
-      <c r="Z20" s="115"/>
-      <c r="AA20" s="115"/>
+      <c r="Y20" s="105"/>
+      <c r="Z20" s="105"/>
+      <c r="AA20" s="105"/>
       <c r="AC20" s="44">
         <v>46387</v>
       </c>
       <c r="AD20" s="38">
         <v>0</v>
       </c>
-      <c r="AE20" s="103">
+      <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20" s="39">
@@ -18276,10 +19518,6 @@
       </c>
     </row>
     <row r="21" spans="2:33" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="78"/>
       <c r="U21" s="35" t="s">
         <v>33</v>
       </c>
@@ -18292,16 +19530,16 @@
       <c r="X21" s="42">
         <v>7084</v>
       </c>
-      <c r="Y21" s="115"/>
-      <c r="Z21" s="115"/>
-      <c r="AA21" s="115"/>
+      <c r="Y21" s="105"/>
+      <c r="Z21" s="105"/>
+      <c r="AA21" s="105"/>
       <c r="AC21" s="40" t="s">
         <v>30</v>
       </c>
       <c r="AD21" s="38">
         <v>11047</v>
       </c>
-      <c r="AE21" s="121">
+      <c r="AE21" s="111">
         <v>11047</v>
       </c>
       <c r="AF21" s="39">
@@ -18322,13 +19560,7 @@
       <c r="E22" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="78"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
+      <c r="G22" s="20"/>
       <c r="U22" s="35" t="s">
         <v>33</v>
       </c>
@@ -18341,16 +19573,16 @@
       <c r="X22" s="42">
         <v>7262</v>
       </c>
-      <c r="Y22" s="115"/>
-      <c r="Z22" s="115"/>
-      <c r="AA22" s="115"/>
+      <c r="Y22" s="105"/>
+      <c r="Z22" s="105"/>
+      <c r="AA22" s="105"/>
       <c r="AC22" s="44">
         <v>46053</v>
       </c>
       <c r="AD22" s="38">
         <v>1505</v>
       </c>
-      <c r="AE22" s="103">
+      <c r="AE22">
         <v>1505</v>
       </c>
       <c r="AF22" s="39">
@@ -18359,25 +19591,19 @@
       <c r="AG22" s="43"/>
     </row>
     <row r="23" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="110">
+      <c r="B23" s="100">
         <v>46053</v>
       </c>
-      <c r="C23" s="111">
+      <c r="C23" s="101">
         <v>151902</v>
       </c>
-      <c r="D23" s="111">
+      <c r="D23" s="101">
         <v>5252</v>
       </c>
-      <c r="E23" s="111">
+      <c r="E23" s="101">
         <v>1505</v>
       </c>
-      <c r="F23" s="78"/>
-      <c r="G23" s="82"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
+      <c r="G23" s="20"/>
       <c r="U23" s="35" t="s">
         <v>33</v>
       </c>
@@ -18390,16 +19616,16 @@
       <c r="X23" s="42">
         <v>5243</v>
       </c>
-      <c r="Y23" s="115"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="115"/>
+      <c r="Y23" s="105"/>
+      <c r="Z23" s="105"/>
+      <c r="AA23" s="105"/>
       <c r="AC23" s="44">
         <v>46081</v>
       </c>
       <c r="AD23" s="38">
         <v>1224</v>
       </c>
-      <c r="AE23" s="103">
+      <c r="AE23">
         <v>1224</v>
       </c>
       <c r="AF23" s="39">
@@ -18410,25 +19636,19 @@
       </c>
     </row>
     <row r="24" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="112">
+      <c r="B24" s="102">
         <v>46081</v>
       </c>
-      <c r="C24" s="113">
+      <c r="C24" s="103">
         <v>50727</v>
       </c>
-      <c r="D24" s="113">
+      <c r="D24" s="103">
         <v>7084</v>
       </c>
-      <c r="E24" s="113">
+      <c r="E24" s="103">
         <v>1224</v>
       </c>
-      <c r="F24" s="78"/>
-      <c r="G24" s="82"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
+      <c r="G24" s="20"/>
       <c r="U24" s="35" t="s">
         <v>33</v>
       </c>
@@ -18441,16 +19661,16 @@
       <c r="X24" s="42">
         <v>4215</v>
       </c>
-      <c r="Y24" s="115"/>
-      <c r="Z24" s="115"/>
-      <c r="AA24" s="115"/>
+      <c r="Y24" s="105"/>
+      <c r="Z24" s="105"/>
+      <c r="AA24" s="105"/>
       <c r="AC24" s="44">
         <v>46112</v>
       </c>
       <c r="AD24" s="38">
         <v>1970</v>
       </c>
-      <c r="AE24" s="103">
+      <c r="AE24">
         <v>1970</v>
       </c>
       <c r="AF24" s="39">
@@ -18461,25 +19681,19 @@
       </c>
     </row>
     <row r="25" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="112">
+      <c r="B25" s="102">
         <v>46112</v>
       </c>
-      <c r="C25" s="113">
+      <c r="C25" s="103">
         <v>175830</v>
       </c>
-      <c r="D25" s="113">
+      <c r="D25" s="103">
         <v>7262</v>
       </c>
-      <c r="E25" s="113">
+      <c r="E25" s="103">
         <v>1970</v>
       </c>
-      <c r="F25" s="78"/>
-      <c r="G25" s="82"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="78"/>
-      <c r="K25" s="78"/>
-      <c r="L25" s="78"/>
+      <c r="G25" s="20"/>
       <c r="U25" s="35" t="s">
         <v>33</v>
       </c>
@@ -18492,16 +19706,16 @@
       <c r="X25" s="42">
         <v>3141</v>
       </c>
-      <c r="Y25" s="115"/>
-      <c r="Z25" s="115"/>
-      <c r="AA25" s="115"/>
+      <c r="Y25" s="105"/>
+      <c r="Z25" s="105"/>
+      <c r="AA25" s="105"/>
       <c r="AC25" s="44">
         <v>46142</v>
       </c>
       <c r="AD25" s="38">
         <v>1546</v>
       </c>
-      <c r="AE25" s="103">
+      <c r="AE25">
         <v>1546</v>
       </c>
       <c r="AF25" s="39">
@@ -18512,25 +19726,19 @@
       </c>
     </row>
     <row r="26" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="112">
+      <c r="B26" s="102">
         <v>46142</v>
       </c>
-      <c r="C26" s="113">
+      <c r="C26" s="103">
         <v>172017</v>
       </c>
-      <c r="D26" s="113">
+      <c r="D26" s="103">
         <v>5243</v>
       </c>
-      <c r="E26" s="113">
+      <c r="E26" s="103">
         <v>1546</v>
       </c>
-      <c r="F26" s="78"/>
-      <c r="G26" s="82"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
+      <c r="G26" s="20"/>
       <c r="U26" s="35" t="s">
         <v>33</v>
       </c>
@@ -18543,16 +19751,16 @@
       <c r="X26" s="42">
         <v>1639</v>
       </c>
-      <c r="Y26" s="115"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="115"/>
+      <c r="Y26" s="105"/>
+      <c r="Z26" s="105"/>
+      <c r="AA26" s="105"/>
       <c r="AC26" s="44">
         <v>46173</v>
       </c>
       <c r="AD26" s="38">
         <v>1667</v>
       </c>
-      <c r="AE26" s="103">
+      <c r="AE26">
         <v>1667</v>
       </c>
       <c r="AF26" s="39">
@@ -18563,25 +19771,19 @@
       </c>
     </row>
     <row r="27" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="112">
+      <c r="B27" s="102">
         <v>46173</v>
       </c>
-      <c r="C27" s="113">
+      <c r="C27" s="103">
         <v>210289</v>
       </c>
-      <c r="D27" s="113">
+      <c r="D27" s="103">
         <v>4215</v>
       </c>
-      <c r="E27" s="113">
+      <c r="E27" s="103">
         <v>1667</v>
       </c>
-      <c r="F27" s="78"/>
-      <c r="G27" s="82"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
+      <c r="G27" s="20"/>
       <c r="U27" s="35" t="s">
         <v>33</v>
       </c>
@@ -18594,16 +19796,16 @@
       <c r="X27" s="42">
         <v>0</v>
       </c>
-      <c r="Y27" s="115"/>
-      <c r="Z27" s="115"/>
-      <c r="AA27" s="115"/>
+      <c r="Y27" s="105"/>
+      <c r="Z27" s="105"/>
+      <c r="AA27" s="105"/>
       <c r="AC27" s="44">
         <v>46203</v>
       </c>
       <c r="AD27" s="38">
         <v>1518</v>
       </c>
-      <c r="AE27" s="103">
+      <c r="AE27">
         <v>1518</v>
       </c>
       <c r="AF27" s="39">
@@ -18614,25 +19816,19 @@
       </c>
     </row>
     <row r="28" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="112">
+      <c r="B28" s="102">
         <v>46203</v>
       </c>
-      <c r="C28" s="113">
+      <c r="C28" s="103">
         <v>169129</v>
       </c>
-      <c r="D28" s="113">
+      <c r="D28" s="103">
         <v>3141</v>
       </c>
-      <c r="E28" s="113">
+      <c r="E28" s="103">
         <v>1518</v>
       </c>
-      <c r="F28" s="78"/>
-      <c r="G28" s="82"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="78"/>
-      <c r="L28" s="78"/>
+      <c r="G28" s="20"/>
       <c r="U28" s="35" t="s">
         <v>33</v>
       </c>
@@ -18645,16 +19841,16 @@
       <c r="X28" s="42">
         <v>0</v>
       </c>
-      <c r="Y28" s="115"/>
-      <c r="Z28" s="115"/>
-      <c r="AA28" s="115"/>
+      <c r="Y28" s="105"/>
+      <c r="Z28" s="105"/>
+      <c r="AA28" s="105"/>
       <c r="AC28" s="44">
         <v>46234</v>
       </c>
       <c r="AD28" s="38">
         <v>825</v>
       </c>
-      <c r="AE28" s="103">
+      <c r="AE28">
         <v>825</v>
       </c>
       <c r="AF28" s="39">
@@ -18665,25 +19861,19 @@
       </c>
     </row>
     <row r="29" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="112">
+      <c r="B29" s="102">
         <v>46234</v>
       </c>
-      <c r="C29" s="113">
+      <c r="C29" s="103">
         <v>28845</v>
       </c>
-      <c r="D29" s="113">
+      <c r="D29" s="103">
         <v>1639</v>
       </c>
-      <c r="E29" s="113">
+      <c r="E29" s="103">
         <v>825</v>
       </c>
-      <c r="F29" s="78"/>
-      <c r="G29" s="82"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="78"/>
-      <c r="L29" s="78"/>
+      <c r="G29" s="20"/>
       <c r="U29" s="35" t="s">
         <v>33</v>
       </c>
@@ -18696,16 +19886,16 @@
       <c r="X29" s="42">
         <v>0</v>
       </c>
-      <c r="Y29" s="115"/>
-      <c r="Z29" s="115"/>
-      <c r="AA29" s="115"/>
+      <c r="Y29" s="105"/>
+      <c r="Z29" s="105"/>
+      <c r="AA29" s="105"/>
       <c r="AC29" s="44">
         <v>46265</v>
       </c>
       <c r="AD29" s="38">
         <v>792</v>
       </c>
-      <c r="AE29" s="103">
+      <c r="AE29">
         <v>792</v>
       </c>
       <c r="AF29" s="39">
@@ -18716,25 +19906,19 @@
       </c>
     </row>
     <row r="30" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="112">
+      <c r="B30" s="102">
         <v>46265</v>
       </c>
-      <c r="C30" s="113">
+      <c r="C30" s="103">
         <v>39741</v>
       </c>
-      <c r="D30" s="113">
+      <c r="D30" s="103">
         <v>0</v>
       </c>
-      <c r="E30" s="113">
+      <c r="E30" s="103">
         <v>792</v>
       </c>
-      <c r="F30" s="78"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="78"/>
-      <c r="K30" s="78"/>
-      <c r="L30" s="78"/>
+      <c r="G30" s="20"/>
       <c r="U30" s="35" t="s">
         <v>33</v>
       </c>
@@ -18747,16 +19931,16 @@
       <c r="X30" s="42">
         <v>0</v>
       </c>
-      <c r="Y30" s="115"/>
-      <c r="Z30" s="115"/>
-      <c r="AA30" s="115"/>
+      <c r="Y30" s="105"/>
+      <c r="Z30" s="105"/>
+      <c r="AA30" s="105"/>
       <c r="AC30" s="44">
         <v>46295</v>
       </c>
       <c r="AD30" s="38">
         <v>0</v>
       </c>
-      <c r="AE30" s="103">
+      <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30" s="39">
@@ -18767,25 +19951,19 @@
       </c>
     </row>
     <row r="31" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="112">
+      <c r="B31" s="102">
         <v>46295</v>
       </c>
-      <c r="C31" s="113">
+      <c r="C31" s="103">
         <v>0</v>
       </c>
-      <c r="D31" s="113">
+      <c r="D31" s="103">
         <v>0</v>
       </c>
-      <c r="E31" s="113">
+      <c r="E31" s="103">
         <v>0</v>
       </c>
-      <c r="F31" s="78"/>
-      <c r="G31" s="82"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="78"/>
+      <c r="G31" s="20"/>
       <c r="U31" s="35" t="s">
         <v>33</v>
       </c>
@@ -18798,16 +19976,16 @@
       <c r="X31" s="42">
         <v>0</v>
       </c>
-      <c r="Y31" s="115"/>
-      <c r="Z31" s="115"/>
-      <c r="AA31" s="115"/>
+      <c r="Y31" s="105"/>
+      <c r="Z31" s="105"/>
+      <c r="AA31" s="105"/>
       <c r="AC31" s="44">
         <v>46326</v>
       </c>
       <c r="AD31" s="38">
         <v>0</v>
       </c>
-      <c r="AE31" s="103">
+      <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31" s="39">
@@ -18818,25 +19996,19 @@
       </c>
     </row>
     <row r="32" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="112">
+      <c r="B32" s="102">
         <v>46326</v>
       </c>
-      <c r="C32" s="113">
+      <c r="C32" s="103">
         <v>0</v>
       </c>
-      <c r="D32" s="113">
+      <c r="D32" s="103">
         <v>0</v>
       </c>
-      <c r="E32" s="113">
+      <c r="E32" s="103">
         <v>0</v>
       </c>
-      <c r="F32" s="78"/>
-      <c r="G32" s="82"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="78"/>
-      <c r="K32" s="78"/>
-      <c r="L32" s="78"/>
+      <c r="G32" s="20"/>
       <c r="U32" s="35" t="s">
         <v>30</v>
       </c>
@@ -18849,16 +20021,16 @@
       <c r="X32" s="42">
         <v>1505</v>
       </c>
-      <c r="Y32" s="115"/>
-      <c r="Z32" s="115"/>
-      <c r="AA32" s="115"/>
+      <c r="Y32" s="105"/>
+      <c r="Z32" s="105"/>
+      <c r="AA32" s="105"/>
       <c r="AC32" s="44">
         <v>46356</v>
       </c>
       <c r="AD32" s="38">
         <v>0</v>
       </c>
-      <c r="AE32" s="103">
+      <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32" s="39">
@@ -18869,25 +20041,19 @@
       </c>
     </row>
     <row r="33" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="112">
+      <c r="B33" s="102">
         <v>46356</v>
       </c>
-      <c r="C33" s="113">
+      <c r="C33" s="103">
         <v>0</v>
       </c>
-      <c r="D33" s="113">
+      <c r="D33" s="103">
         <v>0</v>
       </c>
-      <c r="E33" s="113">
+      <c r="E33" s="103">
         <v>0</v>
       </c>
-      <c r="F33" s="78"/>
-      <c r="G33" s="82"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
-      <c r="L33" s="78"/>
+      <c r="G33" s="20"/>
       <c r="U33" s="35" t="s">
         <v>30</v>
       </c>
@@ -18900,16 +20066,16 @@
       <c r="X33" s="42">
         <v>1224</v>
       </c>
-      <c r="Y33" s="115"/>
-      <c r="Z33" s="115"/>
-      <c r="AA33" s="115"/>
+      <c r="Y33" s="105"/>
+      <c r="Z33" s="105"/>
+      <c r="AA33" s="105"/>
       <c r="AC33" s="44">
         <v>46387</v>
       </c>
       <c r="AD33" s="38">
         <v>0</v>
       </c>
-      <c r="AE33" s="103">
+      <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33" s="39">
@@ -18920,25 +20086,19 @@
       </c>
     </row>
     <row r="34" spans="2:33" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B34" s="112">
+      <c r="B34" s="102">
         <v>46387</v>
       </c>
-      <c r="C34" s="113">
+      <c r="C34" s="103">
         <v>0</v>
       </c>
-      <c r="D34" s="113">
+      <c r="D34" s="103">
         <v>0</v>
       </c>
-      <c r="E34" s="113">
+      <c r="E34" s="103">
         <v>0</v>
       </c>
-      <c r="F34" s="78"/>
-      <c r="G34" s="82"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="78"/>
-      <c r="K34" s="78"/>
-      <c r="L34" s="78"/>
+      <c r="G34" s="20"/>
       <c r="U34" s="35" t="s">
         <v>30</v>
       </c>
@@ -18951,16 +20111,16 @@
       <c r="X34" s="42">
         <v>1970</v>
       </c>
-      <c r="Y34" s="115"/>
-      <c r="Z34" s="115"/>
-      <c r="AA34" s="115"/>
+      <c r="Y34" s="105"/>
+      <c r="Z34" s="105"/>
+      <c r="AA34" s="105"/>
       <c r="AC34" s="40" t="s">
         <v>33</v>
       </c>
       <c r="AD34" s="38">
         <v>33836</v>
       </c>
-      <c r="AE34" s="121">
+      <c r="AE34" s="111">
         <v>33836</v>
       </c>
       <c r="AF34" s="39">
@@ -18969,16 +20129,9 @@
       <c r="AG34" s="43"/>
     </row>
     <row r="35" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C35" s="78"/>
-      <c r="D35" s="80"/>
+      <c r="D35" s="75"/>
       <c r="E35" s="21"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="82"/>
-      <c r="H35" s="78"/>
-      <c r="I35" s="78"/>
-      <c r="J35" s="78"/>
-      <c r="K35" s="78"/>
-      <c r="L35" s="78"/>
+      <c r="G35" s="20"/>
       <c r="U35" s="35" t="s">
         <v>30</v>
       </c>
@@ -18991,16 +20144,16 @@
       <c r="X35" s="42">
         <v>1546</v>
       </c>
-      <c r="Y35" s="115"/>
-      <c r="Z35" s="115"/>
-      <c r="AA35" s="115"/>
+      <c r="Y35" s="105"/>
+      <c r="Z35" s="105"/>
+      <c r="AA35" s="105"/>
       <c r="AC35" s="44">
         <v>46053</v>
       </c>
       <c r="AD35" s="38">
         <v>5252</v>
       </c>
-      <c r="AE35" s="103">
+      <c r="AE35">
         <v>5252</v>
       </c>
       <c r="AF35" s="39">
@@ -19009,16 +20162,9 @@
       <c r="AG35" s="43"/>
     </row>
     <row r="36" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C36" s="78"/>
-      <c r="D36" s="83"/>
+      <c r="D36" s="77"/>
       <c r="E36" s="21"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="82"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="78"/>
-      <c r="K36" s="78"/>
-      <c r="L36" s="78"/>
+      <c r="G36" s="20"/>
       <c r="U36" s="35" t="s">
         <v>30</v>
       </c>
@@ -19031,16 +20177,16 @@
       <c r="X36" s="42">
         <v>1667</v>
       </c>
-      <c r="Y36" s="115"/>
-      <c r="Z36" s="115"/>
-      <c r="AA36" s="115"/>
+      <c r="Y36" s="105"/>
+      <c r="Z36" s="105"/>
+      <c r="AA36" s="105"/>
       <c r="AC36" s="44">
         <v>46081</v>
       </c>
       <c r="AD36" s="38">
         <v>7084</v>
       </c>
-      <c r="AE36" s="103">
+      <c r="AE36">
         <v>7084</v>
       </c>
       <c r="AF36" s="39">
@@ -19051,16 +20197,9 @@
       </c>
     </row>
     <row r="37" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C37" s="78"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="85"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="78"/>
+      <c r="G37" s="20"/>
       <c r="U37" s="35" t="s">
         <v>30</v>
       </c>
@@ -19073,16 +20212,16 @@
       <c r="X37" s="42">
         <v>1518</v>
       </c>
-      <c r="Y37" s="115"/>
-      <c r="Z37" s="115"/>
-      <c r="AA37" s="115"/>
+      <c r="Y37" s="105"/>
+      <c r="Z37" s="105"/>
+      <c r="AA37" s="105"/>
       <c r="AC37" s="44">
         <v>46112</v>
       </c>
       <c r="AD37" s="38">
         <v>7262</v>
       </c>
-      <c r="AE37" s="103">
+      <c r="AE37">
         <v>7262</v>
       </c>
       <c r="AF37" s="39">
@@ -19093,16 +20232,9 @@
       </c>
     </row>
     <row r="38" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C38" s="78"/>
-      <c r="D38" s="83"/>
+      <c r="D38" s="77"/>
       <c r="E38" s="21"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="82"/>
-      <c r="H38" s="78"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="78"/>
+      <c r="G38" s="20"/>
       <c r="U38" s="35" t="s">
         <v>30</v>
       </c>
@@ -19115,16 +20247,16 @@
       <c r="X38" s="42">
         <v>825</v>
       </c>
-      <c r="Y38" s="115"/>
-      <c r="Z38" s="115"/>
-      <c r="AA38" s="115"/>
+      <c r="Y38" s="105"/>
+      <c r="Z38" s="105"/>
+      <c r="AA38" s="105"/>
       <c r="AC38" s="44">
         <v>46142</v>
       </c>
       <c r="AD38" s="38">
         <v>5243</v>
       </c>
-      <c r="AE38" s="103">
+      <c r="AE38">
         <v>5243</v>
       </c>
       <c r="AF38" s="39">
@@ -19135,16 +20267,9 @@
       </c>
     </row>
     <row r="39" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C39" s="78"/>
-      <c r="D39" s="83"/>
+      <c r="D39" s="77"/>
       <c r="E39" s="21"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="82"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="78"/>
-      <c r="K39" s="78"/>
-      <c r="L39" s="78"/>
+      <c r="G39" s="20"/>
       <c r="U39" s="35" t="s">
         <v>30</v>
       </c>
@@ -19157,16 +20282,16 @@
       <c r="X39" s="42">
         <v>792</v>
       </c>
-      <c r="Y39" s="115"/>
-      <c r="Z39" s="115"/>
-      <c r="AA39" s="115"/>
+      <c r="Y39" s="105"/>
+      <c r="Z39" s="105"/>
+      <c r="AA39" s="105"/>
       <c r="AC39" s="44">
         <v>46173</v>
       </c>
       <c r="AD39" s="38">
         <v>4215</v>
       </c>
-      <c r="AE39" s="103">
+      <c r="AE39">
         <v>4215</v>
       </c>
       <c r="AF39" s="39">
@@ -19177,16 +20302,9 @@
       </c>
     </row>
     <row r="40" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C40" s="78"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="85"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="78"/>
-      <c r="L40" s="78"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="78"/>
+      <c r="G40" s="20"/>
       <c r="U40" s="35" t="s">
         <v>30</v>
       </c>
@@ -19199,16 +20317,16 @@
       <c r="X40" s="42">
         <v>0</v>
       </c>
-      <c r="Y40" s="115"/>
-      <c r="Z40" s="115"/>
-      <c r="AA40" s="115"/>
+      <c r="Y40" s="105"/>
+      <c r="Z40" s="105"/>
+      <c r="AA40" s="105"/>
       <c r="AC40" s="44">
         <v>46203</v>
       </c>
       <c r="AD40" s="38">
         <v>3141</v>
       </c>
-      <c r="AE40" s="103">
+      <c r="AE40">
         <v>3141</v>
       </c>
       <c r="AF40" s="39">
@@ -19219,16 +20337,9 @@
       </c>
     </row>
     <row r="41" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C41" s="78"/>
-      <c r="D41" s="83"/>
+      <c r="D41" s="77"/>
       <c r="E41" s="21"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="82"/>
-      <c r="H41" s="78"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="78"/>
-      <c r="K41" s="78"/>
-      <c r="L41" s="78"/>
+      <c r="G41" s="20"/>
       <c r="U41" s="35" t="s">
         <v>30</v>
       </c>
@@ -19241,16 +20352,16 @@
       <c r="X41" s="42">
         <v>0</v>
       </c>
-      <c r="Y41" s="115"/>
-      <c r="Z41" s="115"/>
-      <c r="AA41" s="115"/>
+      <c r="Y41" s="105"/>
+      <c r="Z41" s="105"/>
+      <c r="AA41" s="105"/>
       <c r="AC41" s="44">
         <v>46234</v>
       </c>
       <c r="AD41" s="38">
         <v>1639</v>
       </c>
-      <c r="AE41" s="103">
+      <c r="AE41">
         <v>1639</v>
       </c>
       <c r="AF41" s="39">
@@ -19261,16 +20372,9 @@
       </c>
     </row>
     <row r="42" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C42" s="78"/>
-      <c r="D42" s="83"/>
+      <c r="D42" s="77"/>
       <c r="E42" s="21"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="82"/>
-      <c r="H42" s="78"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="78"/>
-      <c r="K42" s="78"/>
-      <c r="L42" s="78"/>
+      <c r="G42" s="20"/>
       <c r="U42" s="35" t="s">
         <v>30</v>
       </c>
@@ -19283,16 +20387,16 @@
       <c r="X42" s="42">
         <v>0</v>
       </c>
-      <c r="Y42" s="115"/>
-      <c r="Z42" s="115"/>
-      <c r="AA42" s="115"/>
+      <c r="Y42" s="105"/>
+      <c r="Z42" s="105"/>
+      <c r="AA42" s="105"/>
       <c r="AC42" s="44">
         <v>46265</v>
       </c>
       <c r="AD42" s="38">
         <v>0</v>
       </c>
-      <c r="AE42" s="103">
+      <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42" s="39">
@@ -19303,16 +20407,9 @@
       </c>
     </row>
     <row r="43" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C43" s="78"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="85"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="82"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="78"/>
-      <c r="L43" s="78"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="78"/>
+      <c r="G43" s="20"/>
       <c r="U43" s="35" t="s">
         <v>30</v>
       </c>
@@ -19325,16 +20422,16 @@
       <c r="X43" s="42">
         <v>0</v>
       </c>
-      <c r="Y43" s="115"/>
-      <c r="Z43" s="115"/>
-      <c r="AA43" s="115"/>
+      <c r="Y43" s="105"/>
+      <c r="Z43" s="105"/>
+      <c r="AA43" s="105"/>
       <c r="AC43" s="44">
         <v>46295</v>
       </c>
       <c r="AD43" s="38">
         <v>0</v>
       </c>
-      <c r="AE43" s="103">
+      <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43" s="39">
@@ -19345,23 +20442,16 @@
       </c>
     </row>
     <row r="44" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C44" s="78"/>
-      <c r="D44" s="83"/>
+      <c r="D44" s="77"/>
       <c r="E44" s="21"/>
-      <c r="F44" s="78"/>
-      <c r="G44" s="82"/>
-      <c r="H44" s="78"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="78"/>
-      <c r="K44" s="78"/>
-      <c r="L44" s="78"/>
+      <c r="G44" s="20"/>
       <c r="AC44" s="44">
         <v>46326</v>
       </c>
       <c r="AD44" s="38">
         <v>0</v>
       </c>
-      <c r="AE44" s="103">
+      <c r="AE44">
         <v>0</v>
       </c>
       <c r="AF44" s="39">
@@ -19372,23 +20462,16 @@
       </c>
     </row>
     <row r="45" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C45" s="78"/>
-      <c r="D45" s="83"/>
+      <c r="D45" s="77"/>
       <c r="E45" s="21"/>
-      <c r="F45" s="78"/>
-      <c r="G45" s="82"/>
-      <c r="H45" s="78"/>
-      <c r="I45" s="78"/>
-      <c r="J45" s="78"/>
-      <c r="K45" s="78"/>
-      <c r="L45" s="78"/>
+      <c r="G45" s="20"/>
       <c r="AC45" s="44">
         <v>46356</v>
       </c>
       <c r="AD45" s="38">
         <v>0</v>
       </c>
-      <c r="AE45" s="103">
+      <c r="AE45">
         <v>0</v>
       </c>
       <c r="AF45" s="39">
@@ -19399,23 +20482,16 @@
       </c>
     </row>
     <row r="46" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C46" s="78"/>
-      <c r="D46" s="80"/>
+      <c r="D46" s="75"/>
       <c r="E46" s="21"/>
-      <c r="F46" s="78"/>
-      <c r="G46" s="82"/>
-      <c r="H46" s="78"/>
-      <c r="I46" s="78"/>
-      <c r="J46" s="78"/>
-      <c r="K46" s="78"/>
-      <c r="L46" s="78"/>
+      <c r="G46" s="20"/>
       <c r="AC46" s="44">
         <v>46387</v>
       </c>
       <c r="AD46" s="38">
         <v>0</v>
       </c>
-      <c r="AE46" s="103">
+      <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46" s="39">
@@ -19426,172 +20502,43 @@
       </c>
     </row>
     <row r="47" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C47" s="78"/>
-      <c r="D47" s="83"/>
+      <c r="D47" s="77"/>
       <c r="E47" s="21"/>
-      <c r="F47" s="78"/>
-      <c r="G47" s="82"/>
-      <c r="H47" s="78"/>
-      <c r="I47" s="78"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="78"/>
-      <c r="L47" s="78"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" spans="2:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C48" s="78"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="85"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="78"/>
-      <c r="I48" s="78"/>
-      <c r="J48" s="78"/>
-      <c r="K48" s="78"/>
-      <c r="L48" s="78"/>
-    </row>
-    <row r="49" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C49" s="78"/>
-      <c r="D49" s="83"/>
+      <c r="D48" s="77"/>
+      <c r="E48" s="78"/>
+      <c r="G48" s="20"/>
+    </row>
+    <row r="49" spans="4:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D49" s="77"/>
       <c r="E49" s="21"/>
-      <c r="F49" s="78"/>
-      <c r="G49" s="82"/>
-      <c r="H49" s="78"/>
-      <c r="I49" s="78"/>
-      <c r="J49" s="78"/>
-      <c r="K49" s="78"/>
-      <c r="L49" s="78"/>
-    </row>
-    <row r="50" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C50" s="78"/>
-      <c r="D50" s="83"/>
+      <c r="G49" s="20"/>
+    </row>
+    <row r="50" spans="4:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D50" s="77"/>
       <c r="E50" s="21"/>
-      <c r="F50" s="78"/>
-      <c r="G50" s="82"/>
-      <c r="H50" s="78"/>
-      <c r="I50" s="78"/>
-      <c r="J50" s="78"/>
-      <c r="K50" s="78"/>
-      <c r="L50" s="78"/>
-    </row>
-    <row r="51" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C51" s="78"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="85"/>
-      <c r="F51" s="78"/>
-      <c r="G51" s="82"/>
-      <c r="H51" s="78"/>
-      <c r="I51" s="78"/>
-      <c r="J51" s="78"/>
-      <c r="K51" s="78"/>
-      <c r="L51" s="78"/>
-    </row>
-    <row r="52" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C52" s="78"/>
-      <c r="D52" s="78"/>
+      <c r="G50" s="20"/>
+    </row>
+    <row r="51" spans="4:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D51" s="77"/>
+      <c r="E51" s="78"/>
+      <c r="G51" s="20"/>
+    </row>
+    <row r="52" spans="4:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E52" s="21"/>
-      <c r="F52" s="78"/>
-      <c r="G52" s="82"/>
-      <c r="H52" s="78"/>
-      <c r="I52" s="78"/>
-      <c r="J52" s="78"/>
-      <c r="K52" s="78"/>
-      <c r="L52" s="78"/>
-    </row>
-    <row r="53" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C53" s="78"/>
-      <c r="D53" s="83"/>
+      <c r="G52" s="20"/>
+    </row>
+    <row r="53" spans="4:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D53" s="77"/>
       <c r="E53" s="21"/>
-      <c r="F53" s="78"/>
-      <c r="G53" s="82"/>
-      <c r="H53" s="78"/>
-      <c r="I53" s="78"/>
-      <c r="J53" s="78"/>
-      <c r="K53" s="78"/>
-      <c r="L53" s="78"/>
-    </row>
-    <row r="54" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C54" s="78"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="85"/>
-      <c r="F54" s="78"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="78"/>
-      <c r="I54" s="78"/>
-      <c r="J54" s="78"/>
-      <c r="K54" s="78"/>
-      <c r="L54" s="78"/>
-    </row>
-    <row r="55" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C55" s="78"/>
-      <c r="D55" s="78"/>
-      <c r="E55" s="78"/>
-      <c r="F55" s="78"/>
-      <c r="G55" s="78"/>
-      <c r="H55" s="78"/>
-      <c r="I55" s="78"/>
-      <c r="J55" s="78"/>
-      <c r="K55" s="78"/>
-      <c r="L55" s="78"/>
-    </row>
-    <row r="56" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C56" s="78"/>
-      <c r="D56" s="78"/>
-      <c r="E56" s="78"/>
-      <c r="F56" s="78"/>
-      <c r="G56" s="78"/>
-      <c r="H56" s="78"/>
-      <c r="I56" s="78"/>
-      <c r="J56" s="78"/>
-      <c r="K56" s="78"/>
-      <c r="L56" s="78"/>
-    </row>
-    <row r="57" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C57" s="78"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
-      <c r="G57" s="78"/>
-      <c r="H57" s="78"/>
-      <c r="I57" s="78"/>
-      <c r="J57" s="78"/>
-      <c r="K57" s="78"/>
-      <c r="L57" s="78"/>
-    </row>
-    <row r="58" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C58" s="78"/>
-      <c r="D58" s="78"/>
-      <c r="E58" s="78"/>
-      <c r="F58" s="78"/>
-      <c r="G58" s="78"/>
-      <c r="H58" s="78"/>
-      <c r="I58" s="78"/>
-      <c r="J58" s="78"/>
-      <c r="K58" s="78"/>
-      <c r="L58" s="78"/>
-    </row>
-    <row r="59" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C59" s="78"/>
-      <c r="D59" s="78"/>
-      <c r="E59" s="78"/>
-      <c r="F59" s="78"/>
-      <c r="G59" s="78"/>
-      <c r="H59" s="78"/>
-      <c r="I59" s="78"/>
-      <c r="J59" s="78"/>
-      <c r="K59" s="78"/>
-      <c r="L59" s="78"/>
-    </row>
-    <row r="60" spans="3:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C60" s="78"/>
-      <c r="D60" s="78"/>
-      <c r="E60" s="78"/>
-      <c r="F60" s="78"/>
-      <c r="G60" s="78"/>
-      <c r="H60" s="78"/>
-      <c r="I60" s="78"/>
-      <c r="J60" s="78"/>
-      <c r="K60" s="78"/>
-      <c r="L60" s="78"/>
+      <c r="G53" s="20"/>
+    </row>
+    <row r="54" spans="4:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D54" s="77"/>
+      <c r="E54" s="78"/>
+      <c r="G54" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting pivot="1" sqref="AE9:AE20">
@@ -19816,4 +20763,790 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14CBC790-D312-4E13-A38A-F5FE6ADE448A}">
+  <dimension ref="B2:G38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="56.6640625" customWidth="1"/>
+    <col min="4" max="4" width="77.6640625" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="B2" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="115" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="115" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="116" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="117" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="121">
+        <v>46053</v>
+      </c>
+      <c r="G3" s="122">
+        <v>151902</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="121">
+        <v>46081</v>
+      </c>
+      <c r="G4" s="122">
+        <v>50727</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="121">
+        <v>46112</v>
+      </c>
+      <c r="G5" s="122">
+        <v>175830</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="121">
+        <v>46142</v>
+      </c>
+      <c r="G6" s="122">
+        <v>172017</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="121">
+        <v>46173</v>
+      </c>
+      <c r="G7" s="122">
+        <v>210289</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="121">
+        <v>46203</v>
+      </c>
+      <c r="G8" s="122">
+        <v>169129</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="121">
+        <v>46234</v>
+      </c>
+      <c r="G9" s="122">
+        <v>28845</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="121">
+        <v>46265</v>
+      </c>
+      <c r="G10" s="122">
+        <v>39741</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="121">
+        <v>46295</v>
+      </c>
+      <c r="G11" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="121">
+        <v>46326</v>
+      </c>
+      <c r="G12" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="121">
+        <v>46356</v>
+      </c>
+      <c r="G13" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="121">
+        <v>46387</v>
+      </c>
+      <c r="G14" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="121">
+        <v>46053</v>
+      </c>
+      <c r="G15" s="122">
+        <v>5252</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="121">
+        <v>46081</v>
+      </c>
+      <c r="G16" s="122">
+        <v>7084</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="121">
+        <v>46112</v>
+      </c>
+      <c r="G17" s="122">
+        <v>7262</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="121">
+        <v>46142</v>
+      </c>
+      <c r="G18" s="122">
+        <v>5243</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="121">
+        <v>46173</v>
+      </c>
+      <c r="G19" s="122">
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="121">
+        <v>46203</v>
+      </c>
+      <c r="G20" s="122">
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="121">
+        <v>46234</v>
+      </c>
+      <c r="G21" s="122">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="121">
+        <v>46265</v>
+      </c>
+      <c r="G22" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="121">
+        <v>46295</v>
+      </c>
+      <c r="G23" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" s="121">
+        <v>46326</v>
+      </c>
+      <c r="G24" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="121">
+        <v>46356</v>
+      </c>
+      <c r="G25" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="121">
+        <v>46387</v>
+      </c>
+      <c r="G26" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="121">
+        <v>46053</v>
+      </c>
+      <c r="G27" s="122">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="121">
+        <v>46081</v>
+      </c>
+      <c r="G28" s="122">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="121">
+        <v>46112</v>
+      </c>
+      <c r="G29" s="122">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="121">
+        <v>46142</v>
+      </c>
+      <c r="G30" s="122">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="121">
+        <v>46173</v>
+      </c>
+      <c r="G31" s="122">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="121">
+        <v>46203</v>
+      </c>
+      <c r="G32" s="122">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="121">
+        <v>46234</v>
+      </c>
+      <c r="G33" s="122">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F34" s="121">
+        <v>46265</v>
+      </c>
+      <c r="G34" s="122">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" s="121">
+        <v>46295</v>
+      </c>
+      <c r="G35" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="121">
+        <v>46326</v>
+      </c>
+      <c r="G36" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="121">
+        <v>46356</v>
+      </c>
+      <c r="G37" s="122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="124" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="125" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="125" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="126">
+        <v>46387</v>
+      </c>
+      <c r="G38" s="127">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1510A4F-D25B-47BA-A89B-1851FE309F8C}">
+  <dimension ref="C39:D44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="39" spans="3:4" ht="33" x14ac:dyDescent="0.45">
+      <c r="D39" s="129" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" ht="33.75" x14ac:dyDescent="0.5">
+      <c r="D40" s="129" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C44" s="128"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/public/assets/files/Excel_Demo-02/SISB_USEP_DEMO-2.xlsx
+++ b/public/assets/files/Excel_Demo-02/SISB_USEP_DEMO-2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1375" documentId="8_{B86F2B6C-3DE1-486D-B3D3-0A1863A11CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{966E1D2C-4C9B-4407-92F6-8667675C4E53}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{537DF2C6-54A6-4649-8875-CD01F068054D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{537DF2C6-54A6-4649-8875-CD01F068054D}"/>
   </bookViews>
   <sheets>
     <sheet name="USEP_2026" sheetId="6" r:id="rId1"/>
@@ -33,6 +33,7 @@
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId10"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1065,31 +1066,31 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1104,15 +1105,6 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{D0C2D436-22CC-4622-BFAB-EE73B1162312}"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1282,6 +1274,45 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1320,36 +1351,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -15658,65 +15659,17 @@
     </format>
   </formats>
   <conditionalFormats count="12">
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="12">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
             <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
+              <x v="1"/>
             </reference>
             <reference field="0" count="1" selected="0">
-              <x v="2"/>
+              <x v="0"/>
             </reference>
-            <reference field="2" count="8">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="2">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-            <reference field="2" count="8">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="3">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="2" count="9">
+            <reference field="2" count="12">
               <x v="0"/>
               <x v="1"/>
               <x v="2"/>
@@ -15726,22 +15679,25 @@
               <x v="6"/>
               <x v="7"/>
               <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
             </reference>
           </references>
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="4">
+    <conditionalFormat priority="11">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
             <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
+              <x v="1"/>
             </reference>
             <reference field="0" count="1" selected="0">
               <x v="1"/>
             </reference>
-            <reference field="2" count="9">
+            <reference field="2" count="12">
               <x v="0"/>
               <x v="1"/>
               <x v="2"/>
@@ -15751,22 +15707,25 @@
               <x v="6"/>
               <x v="7"/>
               <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
             </reference>
           </references>
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="5">
+    <conditionalFormat priority="10">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
             <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
+              <x v="1"/>
             </reference>
             <reference field="0" count="1" selected="0">
-              <x v="0"/>
+              <x v="2"/>
             </reference>
-            <reference field="2" count="9">
+            <reference field="2" count="12">
               <x v="0"/>
               <x v="1"/>
               <x v="2"/>
@@ -15776,37 +15735,15 @@
               <x v="6"/>
               <x v="7"/>
               <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
             </reference>
           </references>
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="6">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="2" count="9">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="7">
+    <conditionalFormat priority="9">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -15814,7 +15751,7 @@
               <x v="1"/>
             </reference>
             <reference field="0" count="1" selected="0">
-              <x v="2"/>
+              <x v="0"/>
             </reference>
             <reference field="2" count="12">
               <x v="0"/>
@@ -15862,35 +15799,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="9">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="2" count="12">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="10">
+    <conditionalFormat priority="7">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -15918,17 +15827,17 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="11">
+    <conditionalFormat priority="6">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
             <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
+              <x v="3"/>
             </reference>
             <reference field="0" count="1" selected="0">
-              <x v="1"/>
+              <x v="0"/>
             </reference>
-            <reference field="2" count="12">
+            <reference field="2" count="9">
               <x v="0"/>
               <x v="1"/>
               <x v="2"/>
@@ -15938,25 +15847,22 @@
               <x v="6"/>
               <x v="7"/>
               <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
             </reference>
           </references>
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="12">
+    <conditionalFormat priority="5">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
             <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
+              <x v="3"/>
             </reference>
             <reference field="0" count="1" selected="0">
               <x v="0"/>
             </reference>
-            <reference field="2" count="12">
+            <reference field="2" count="9">
               <x v="0"/>
               <x v="1"/>
               <x v="2"/>
@@ -15966,9 +15872,104 @@
               <x v="6"/>
               <x v="7"/>
               <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="4">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="9">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="3">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="9">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+            <reference field="2" count="8">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+            <reference field="2" count="8">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
             </reference>
           </references>
         </pivotArea>
@@ -15988,7 +15989,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EC91FF0-6FB2-448B-B020-FF75E4912B6E}" name="LongFormat" displayName="LongFormat" ref="B2:G38" totalsRowShown="0" headerRowDxfId="7" dataDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EC91FF0-6FB2-448B-B020-FF75E4912B6E}" name="LongFormat" displayName="LongFormat" ref="B2:G38" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="B2:G38" xr:uid="{9EC91FF0-6FB2-448B-B020-FF75E4912B6E}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -15998,12 +15999,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C3F457BA-E1FD-461F-B39D-B29DC7AF5511}" name="N° Indicateur" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{A854F890-2B20-4D64-B269-231139DE3A94}" name="Indicateur" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{28DB4D8B-FF90-4194-8747-A51F6B5601E3}" name="Descriptif" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{0DC2BAB9-CC31-4FB7-A47D-2F415DC936A9}" name="Équipe" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{C116F4D2-1610-497E-A207-37C7A65204A5}" name="Date" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{CD71C008-A581-4C92-AD38-D292BA862EDC}" name="Valeur" dataDxfId="1" dataCellStyle="Milliers"/>
+    <tableColumn id="1" xr3:uid="{C3F457BA-E1FD-461F-B39D-B29DC7AF5511}" name="N° Indicateur" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{A854F890-2B20-4D64-B269-231139DE3A94}" name="Indicateur" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{28DB4D8B-FF90-4194-8747-A51F6B5601E3}" name="Descriptif" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{0DC2BAB9-CC31-4FB7-A47D-2F415DC936A9}" name="Équipe" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{C116F4D2-1610-497E-A207-37C7A65204A5}" name="Date" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{CD71C008-A581-4C92-AD38-D292BA862EDC}" name="Valeur" dataDxfId="0" dataCellStyle="Milliers"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17064,7 +17065,7 @@
         <v>148897</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>29</v>
       </c>

--- a/public/assets/files/Excel_Demo-02/SISB_USEP_DEMO-2.xlsx
+++ b/public/assets/files/Excel_Demo-02/SISB_USEP_DEMO-2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1375" documentId="8_{B86F2B6C-3DE1-486D-B3D3-0A1863A11CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{966E1D2C-4C9B-4407-92F6-8667675C4E53}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{537DF2C6-54A6-4649-8875-CD01F068054D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{537DF2C6-54A6-4649-8875-CD01F068054D}"/>
   </bookViews>
   <sheets>
     <sheet name="USEP_2026" sheetId="6" r:id="rId1"/>
@@ -31,9 +31,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId10"/>
+    <pivotCache cacheId="6" r:id="rId10"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -14972,7 +14971,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2E4DD02E-837C-429B-90E1-3825EDE2D0C9}" name="Tableau croisé dynamique1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="  ">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2E4DD02E-837C-429B-90E1-3825EDE2D0C9}" name="Tableau croisé dynamique1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="  ">
   <location ref="AC7:AG46" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -15659,7 +15658,211 @@
     </format>
   </formats>
   <conditionalFormats count="12">
-    <conditionalFormat priority="12">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+            <reference field="2" count="8">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+            <reference field="2" count="8">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="3">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="9">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="4">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="9">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="5">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="2" count="9">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="6">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="2" count="9">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="7">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+            <reference field="2" count="12">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="8">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="12">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="9">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -15668,6 +15871,34 @@
             </reference>
             <reference field="0" count="1" selected="0">
               <x v="0"/>
+            </reference>
+            <reference field="2" count="12">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="10">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="0" count="1" selected="0">
+              <x v="2"/>
             </reference>
             <reference field="2" count="12">
               <x v="0"/>
@@ -15715,35 +15946,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="10">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-            <reference field="2" count="12">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="9">
+    <conditionalFormat priority="12">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -15766,210 +15969,6 @@
               <x v="9"/>
               <x v="10"/>
               <x v="11"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="8">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="2" count="12">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="7">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-            <reference field="2" count="12">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="6">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="2" count="9">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="5">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="2" count="9">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="4">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="2" count="9">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="3">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="2" count="9">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="2">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-            <reference field="2" count="8">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="1">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-            <reference field="0" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-            <reference field="2" count="8">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
             </reference>
           </references>
         </pivotArea>
